--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3.198</t>
+          <t>3.305</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.247</t>
+          <t>3.341</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.207</t>
+          <t>3.296</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>3.326</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.435</t>
+          <t>3.511</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4.049</t>
+          <t>4.115</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.454</t>
+          <t>4.513</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4.026</t>
+          <t>4.077</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.202</t>
+          <t>3.246</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2.975</t>
+          <t>3.015</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.957</t>
+          <t>2.987</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.098</t>
+          <t>3.123</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.311</t>
+          <t>3.333</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3.367</t>
+          <t>3.387</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3.344</t>
+          <t>3.362</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.417</t>
+          <t>3.437</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3.674</t>
+          <t>3.686</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.317</t>
+          <t>4.324</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.733</t>
+          <t>4.735</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>4.257</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3.141</t>
+          <t>3.151</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3.279</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3.488</t>
+          <t>3.511</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3.548</t>
+          <t>3.563</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3.528</t>
+          <t>3.533</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3.594</t>
+          <t>3.617</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3.806</t>
+          <t>3.825</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4.394</t>
+          <t>4.410</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1965,7 +1965,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2073,7 +2073,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3045,7 +3045,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -4066,7 +4066,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -4336,7 +4336,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4984,7 +4984,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5416,7 +5416,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5632,7 +5632,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -5816,7 +5816,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6356,7 +6356,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6572,7 +6572,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6680,7 +6680,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6734,7 +6734,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6950,7 +6950,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7647,7 +7647,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7701,7 +7701,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7755,7 +7755,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7782,7 +7782,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7809,7 +7809,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7863,7 +7863,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8025,7 +8025,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8187,7 +8187,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8241,7 +8241,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8295,7 +8295,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8457,7 +8457,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8727,7 +8727,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8781,7 +8781,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8889,7 +8889,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8943,7 +8943,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8997,7 +8997,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -9105,7 +9105,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -9159,7 +9159,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -9370,7 +9370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>42.070</t>
+          <t>42.610</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.648</t>
+          <t>41.775</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -9478,7 +9478,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -9586,7 +9586,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -9640,7 +9640,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9694,7 +9694,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -9802,7 +9802,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -9856,7 +9856,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -9964,7 +9964,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -10018,7 +10018,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -10072,7 +10072,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -10126,7 +10126,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -10180,7 +10180,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -10234,7 +10234,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -10288,7 +10288,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -10342,7 +10342,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -10477,7 +10477,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10504,7 +10504,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10558,7 +10558,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10666,7 +10666,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -10693,7 +10693,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10720,7 +10720,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -10747,7 +10747,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -10774,7 +10774,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -10828,7 +10828,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -11098,7 +11098,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -11152,7 +11152,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -11476,7 +11476,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -11530,7 +11530,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -11584,7 +11584,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -11611,7 +11611,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -11638,7 +11638,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -11692,7 +11692,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -11746,7 +11746,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -12016,7 +12016,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3.305</t>
+          <t>3.287</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.341</t>
+          <t>3.328</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.296</t>
+          <t>3.284</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.326</t>
+          <t>3.316</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.511</t>
+          <t>3.502</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4.115</t>
+          <t>4.105</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.513</t>
+          <t>4.501</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4.077</t>
+          <t>4.076</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3.015</t>
+          <t>3.016</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.987</t>
+          <t>2.989</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.123</t>
+          <t>3.124</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.333</t>
+          <t>3.334</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.437</t>
+          <t>3.432</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.324</t>
+          <t>4.327</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.735</t>
+          <t>4.740</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3.129</t>
+          <t>3.151</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3.287</t>
+          <t>3.285</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.328</t>
+          <t>3.314</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.284</t>
+          <t>3.267</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.316</t>
+          <t>3.299</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.502</t>
+          <t>3.481</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4.105</t>
+          <t>4.084</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.501</t>
+          <t>4.483</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4.076</t>
+          <t>4.051</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.246</t>
+          <t>3.224</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3.016</t>
+          <t>2.994</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.989</t>
+          <t>2.970</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.124</t>
+          <t>3.110</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.334</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3.387</t>
+          <t>3.372</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3.362</t>
+          <t>3.348</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.432</t>
+          <t>3.423</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3.686</t>
+          <t>3.672</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.327</t>
+          <t>4.319</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.740</t>
+          <t>4.733</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3.481</t>
+          <t>3.482</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3.175</t>
+          <t>3.178</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3.151</t>
+          <t>3.158</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.297</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3.511</t>
+          <t>3.512</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3.563</t>
+          <t>3.564</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>3.544</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3.617</t>
+          <t>3.616</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3.825</t>
+          <t>3.823</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4.410</t>
+          <t>4.416</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4.797</t>
+          <t>4.817</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>4.325</t>
+          <t>4.341</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3.104</t>
+          <t>3.160</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3.217</t>
+          <t>3.248</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.556</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>3.765</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3.363</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3.248</t>
+          <t>3.258</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>42.610</t>
+          <t>42.010</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>41.775</t>
+          <t>42.505</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3.285</t>
+          <t>3.288</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.314</t>
+          <t>3.317</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.267</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.299</t>
+          <t>3.304</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.481</t>
+          <t>3.483</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4.084</t>
+          <t>4.088</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.483</t>
+          <t>4.487</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4.051</t>
+          <t>4.058</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.224</t>
+          <t>3.228</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2.994</t>
+          <t>2.998</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>2.975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.110</t>
+          <t>3.114</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.326</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3.372</t>
+          <t>3.379</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3.348</t>
+          <t>3.353</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.423</t>
+          <t>3.427</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3.672</t>
+          <t>3.678</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.319</t>
+          <t>4.324</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.733</t>
+          <t>4.736</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3.288</t>
+          <t>3.224</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.317</t>
+          <t>3.254</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>3.214</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.304</t>
+          <t>3.244</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.483</t>
+          <t>3.428</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4.088</t>
+          <t>4.032</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>4.436</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4.058</t>
+          <t>4.024</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.228</t>
+          <t>3.201</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2.998</t>
+          <t>2.980</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.975</t>
+          <t>2.958</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.114</t>
+          <t>3.098</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.326</t>
+          <t>3.310</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3.379</t>
+          <t>3.362</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3.353</t>
+          <t>3.335</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.427</t>
+          <t>3.408</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3.678</t>
+          <t>3.661</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.324</t>
+          <t>4.312</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.736</t>
+          <t>4.716</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4.257</t>
+          <t>4.248</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3.482</t>
+          <t>3.464</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3.178</t>
+          <t>3.172</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3.158</t>
+          <t>3.145</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3.297</t>
+          <t>3.287</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3.512</t>
+          <t>3.497</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3.564</t>
+          <t>3.556</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3.544</t>
+          <t>3.535</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3.616</t>
+          <t>3.601</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3.823</t>
+          <t>3.812</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4.416</t>
+          <t>4.404</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4.817</t>
+          <t>4.808</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>4.341</t>
+          <t>4.338</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.458</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3.151</t>
+          <t>3.136</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3.160</t>
+          <t>3.110</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3.248</t>
+          <t>3.222</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.434</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>3.498</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3.481</t>
+          <t>3.484</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3.765</t>
+          <t>3.734</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>4.306</t>
+          <t>4.317</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4.729</t>
+          <t>4.740</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4.275</t>
+          <t>4.287</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3.458</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3.043</t>
+          <t>3.052</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3.003</t>
+          <t>3.013</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>3.135</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3.358</t>
+          <t>3.368</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3.397</t>
+          <t>3.407</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3.364</t>
+          <t>3.375</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.451</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3.638</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>4.167</t>
+          <t>4.179</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -1965,7 +1965,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>4.542</t>
+          <t>4.555</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>4.087</t>
+          <t>4.098</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.374</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2.952</t>
+          <t>2.964</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2073,7 +2073,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.919</t>
+          <t>2.931</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3.047</t>
+          <t>3.060</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3.258</t>
+          <t>3.261</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3.304</t>
+          <t>3.319</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.298</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.376</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3.598</t>
+          <t>3.614</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>4.182</t>
+          <t>4.198</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4.510</t>
+          <t>4.525</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>4.047</t>
+          <t>4.062</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>3.289</t>
+          <t>3.304</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>2.834</t>
+          <t>2.849</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2.804</t>
+          <t>2.819</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>2.939</t>
+          <t>2.954</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>3.121</t>
+          <t>3.136</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3.174</t>
+          <t>3.189</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>3.164</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>3.214</t>
+          <t>3.229</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3.429</t>
+          <t>3.444</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>3.954</t>
+          <t>3.969</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4.259</t>
+          <t>4.274</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3.802</t>
+          <t>3.817</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>3.098</t>
+          <t>3.113</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2.737</t>
+          <t>2.752</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2.725</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>2.866</t>
+          <t>2.881</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>3.055</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3.106</t>
+          <t>3.121</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>3.080</t>
+          <t>3.095</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3.153</t>
+          <t>3.168</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>3.392</t>
+          <t>3.407</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3.811</t>
+          <t>3.826</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>4.091</t>
+          <t>4.106</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3.786</t>
+          <t>3.801</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>3.176</t>
+          <t>3.191</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2.756</t>
+          <t>2.771</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3045,7 +3045,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2.746</t>
+          <t>2.761</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>2.896</t>
+          <t>2.911</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>3.076</t>
+          <t>3.091</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>3.136</t>
+          <t>3.151</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>3.151</t>
+          <t>3.166</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>3.197</t>
+          <t>3.212</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>79.85</t>
+          <t>77.90</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>79.51</t>
+          <t>77.52</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>78.82</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>78.12</t>
+          <t>76.41</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>75.87</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>76.81</t>
+          <t>75.36</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76.21</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>75.66</t>
+          <t>74.42</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75.17</t>
+          <t>74.01</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>74.74</t>
+          <t>73.64</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74.35</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>74.00</t>
+          <t>72.97</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73.70</t>
+          <t>72.70</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>73.45</t>
+          <t>72.47</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>73.22</t>
+          <t>72.26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>73.02</t>
+          <t>72.07</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>71.89</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>72.63</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>72.47</t>
+          <t>71.55</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>71.44</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>72.26</t>
+          <t>71.34</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>71.95</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>71.83</t>
+          <t>70.95</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>71.71</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>71.60</t>
+          <t>70.73</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>71.50</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>70.56</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>70.47</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4066,7 +4066,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>71.23</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>71.19</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>71.15</t>
+          <t>70.33</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>71.10</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>70.24</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>70.96</t>
+          <t>70.17</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>70.09</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>70.79</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>70.63</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4336,7 +4336,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>70.56</t>
+          <t>69.80</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>70.47</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>70.39</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>70.31</t>
+          <t>69.64</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>69.59</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>70.19</t>
+          <t>69.54</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>70.13</t>
+          <t>69.47</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>69.39</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>69.97</t>
+          <t>69.31</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>69.91</t>
+          <t>69.27</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>69.81</t>
+          <t>69.20</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>69.00</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>69.60</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>69.56</t>
+          <t>68.93</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>69.52</t>
+          <t>68.90</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>68.85</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>69.43</t>
+          <t>68.79</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4984,7 +4984,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>68.70</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>69.30</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>69.25</t>
+          <t>68.60</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>69.20</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>69.15</t>
+          <t>68.50</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>69.09</t>
+          <t>68.44</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>68.97</t>
+          <t>68.32</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>68.27</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>68.22</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>68.17</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>68.76</t>
+          <t>68.11</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.04</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>67.97</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>67.90</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>68.48</t>
+          <t>67.83</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -5416,7 +5416,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>68.41</t>
+          <t>67.76</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>68.34</t>
+          <t>67.69</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>67.62</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>68.20</t>
+          <t>67.55</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>68.13</t>
+          <t>67.48</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>68.06</t>
+          <t>67.41</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>67.34</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>67.27</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -5632,7 +5632,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>67.20</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>96.690</t>
+          <t>99.940</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>97.070</t>
+          <t>100.090</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98.990</t>
+          <t>102.080</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.160</t>
+          <t>103.230</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5816,7 +5816,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104.020</t>
+          <t>107.230</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>106.300</t>
+          <t>109.230</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>106.640</t>
+          <t>109.530</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>105.030</t>
+          <t>107.820</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>96.710</t>
+          <t>99.290</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>86.100</t>
+          <t>87.460</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80.950</t>
+          <t>82.290</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>77.100</t>
+          <t>77.960</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>76.850</t>
+          <t>77.500</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>77.800</t>
+          <t>78.500</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79.150</t>
+          <t>79.740</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>78.950</t>
+          <t>79.700</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81.850</t>
+          <t>82.600</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>82.910</t>
+          <t>83.790</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>84.850</t>
+          <t>85.340</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>84.900</t>
+          <t>85.480</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>78.620</t>
+          <t>79.270</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>69.360</t>
+          <t>69.560</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>63.990</t>
+          <t>64.140</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>62.650</t>
+          <t>62.790</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -6356,7 +6356,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>61.480</t>
+          <t>61.470</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>61.170</t>
+          <t>61.150</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>62.720</t>
+          <t>62.690</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>68.440</t>
+          <t>68.230</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70.710</t>
+          <t>70.500</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>72.710</t>
+          <t>72.490</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>74.750</t>
+          <t>74.760</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>74.360</t>
+          <t>74.350</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -6572,7 +6572,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>71.830</t>
+          <t>71.500</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>61.400</t>
+          <t>61.470</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>57.040</t>
+          <t>57.080</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>55.640</t>
+          <t>55.740</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -6680,7 +6680,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>56.740</t>
+          <t>56.320</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>56.890</t>
+          <t>56.430</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -6734,7 +6734,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>58.550</t>
+          <t>58.090</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>63.340</t>
+          <t>63.150</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>65.320</t>
+          <t>65.270</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>67.200</t>
+          <t>67.140</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>68.350</t>
+          <t>68.210</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>69.350</t>
+          <t>69.210</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>68.330</t>
+          <t>68.220</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>63.170</t>
+          <t>63.370</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -6950,7 +6950,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>60.380</t>
+          <t>60.580</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>57.790</t>
+          <t>57.980</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>55.460</t>
+          <t>55.650</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>54.090</t>
+          <t>54.280</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>55.110</t>
+          <t>55.280</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>64.170</t>
+          <t>63.890</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>66.750</t>
+          <t>66.470</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>68.670</t>
+          <t>68.370</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>69.410</t>
+          <t>69.330</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>69.740</t>
+          <t>69.660</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>68.230</t>
+          <t>68.150</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>62.820</t>
+          <t>63.440</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>58.720</t>
+          <t>59.340</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>57.110</t>
+          <t>56.740</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>55.800</t>
+          <t>55.310</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>55.090</t>
+          <t>54.600</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>56.110</t>
+          <t>55.620</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>61.430</t>
+          <t>60.940</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>64.100</t>
+          <t>63.600</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>66.660</t>
+          <t>66.160</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7647,7 +7647,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7701,7 +7701,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7755,7 +7755,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7782,7 +7782,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7809,7 +7809,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7863,7 +7863,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8025,7 +8025,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8187,7 +8187,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8241,7 +8241,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8295,7 +8295,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8457,7 +8457,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8727,7 +8727,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8781,7 +8781,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8889,7 +8889,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8943,7 +8943,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8997,7 +8997,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -9105,7 +9105,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -9159,7 +9159,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -9370,7 +9370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>42.010</t>
+          <t>41.480</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>42.505</t>
+          <t>41.635</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -9478,7 +9478,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -9586,7 +9586,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -9640,7 +9640,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9694,7 +9694,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -9802,7 +9802,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -9856,7 +9856,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -9964,7 +9964,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -10018,7 +10018,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -10072,7 +10072,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -10126,7 +10126,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -10180,7 +10180,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -10234,7 +10234,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -10288,7 +10288,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -10342,7 +10342,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -10477,7 +10477,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10504,7 +10504,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10558,7 +10558,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10666,7 +10666,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -10693,7 +10693,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10720,7 +10720,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -10747,7 +10747,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -10774,7 +10774,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -10828,7 +10828,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -11098,7 +11098,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -11152,7 +11152,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -11476,7 +11476,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -11530,7 +11530,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -11584,7 +11584,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -11611,7 +11611,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -11638,7 +11638,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -11692,7 +11692,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -11746,7 +11746,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -12016,7 +12016,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3.224</t>
+          <t>3.169</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.254</t>
+          <t>3.218</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.214</t>
+          <t>3.175</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.244</t>
+          <t>3.208</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.428</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4.032</t>
+          <t>3.994</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.436</t>
+          <t>4.393</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4.024</t>
+          <t>3.975</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.201</t>
+          <t>3.169</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2.980</t>
+          <t>2.957</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.958</t>
+          <t>2.936</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.098</t>
+          <t>3.066</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>3.281</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3.362</t>
+          <t>3.332</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3.335</t>
+          <t>3.305</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.408</t>
+          <t>3.385</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3.661</t>
+          <t>3.636</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.312</t>
+          <t>4.287</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.716</t>
+          <t>4.700</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4.248</t>
+          <t>4.229</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3.464</t>
+          <t>3.443</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3.172</t>
+          <t>3.157</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3.145</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3.287</t>
+          <t>3.276</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3.497</t>
+          <t>3.488</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3.556</t>
+          <t>3.549</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3.535</t>
+          <t>3.529</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3.601</t>
+          <t>3.595</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3.812</t>
+          <t>3.807</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4.404</t>
+          <t>4.399</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4.808</t>
+          <t>4.802</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>4.338</t>
+          <t>4.333</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3.458</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3.136</t>
+          <t>3.126</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3.110</t>
+          <t>3.098</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>3.209</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3.434</t>
+          <t>3.421</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3.498</t>
+          <t>3.485</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3.484</t>
+          <t>3.471</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>3.547</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3.734</t>
+          <t>3.717</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>4.317</t>
+          <t>4.296</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4.740</t>
+          <t>4.718</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4.287</t>
+          <t>4.263</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.446</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3.052</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3.013</t>
+          <t>2.987</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>3.135</t>
+          <t>3.109</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3.368</t>
+          <t>3.342</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>3.382</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3.375</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3.451</t>
+          <t>3.426</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.625</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>4.179</t>
+          <t>4.155</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -1965,7 +1965,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>4.555</t>
+          <t>4.531</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>4.098</t>
+          <t>4.075</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3.374</t>
+          <t>3.352</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2.964</t>
+          <t>2.944</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2073,7 +2073,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.931</t>
+          <t>2.911</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3.060</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3.261</t>
+          <t>3.242</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3.319</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>3.298</t>
+          <t>3.279</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>3.357</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3.614</t>
+          <t>3.595</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>4.198</t>
+          <t>4.179</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4.525</t>
+          <t>4.505</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>4.062</t>
+          <t>4.042</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>3.304</t>
+          <t>3.283</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>2.849</t>
+          <t>2.828</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2.819</t>
+          <t>2.798</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>2.954</t>
+          <t>2.933</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>3.136</t>
+          <t>3.115</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3.189</t>
+          <t>3.168</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>3.164</t>
+          <t>3.143</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>3.229</t>
+          <t>3.208</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3.444</t>
+          <t>3.423</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>3.969</t>
+          <t>3.948</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4.274</t>
+          <t>4.253</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3.817</t>
+          <t>3.796</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>3.113</t>
+          <t>3.092</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2.752</t>
+          <t>2.731</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>2.719</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>2.881</t>
+          <t>2.860</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.049</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3.121</t>
+          <t>3.100</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>3.095</t>
+          <t>3.074</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3.168</t>
+          <t>3.147</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>3.386</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3.826</t>
+          <t>3.805</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>4.106</t>
+          <t>4.085</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3.801</t>
+          <t>3.780</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>3.191</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2.771</t>
+          <t>2.750</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3045,7 +3045,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2.761</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>2.911</t>
+          <t>2.890</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>3.091</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>3.151</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>3.166</t>
+          <t>3.145</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>3.212</t>
+          <t>3.191</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>77.90</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>77.52</t>
+          <t>76.80</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>76.39</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>76.41</t>
+          <t>75.94</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75.87</t>
+          <t>75.48</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.36</t>
+          <t>75.02</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>74.57</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>74.42</t>
+          <t>74.15</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74.01</t>
+          <t>73.77</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>73.64</t>
+          <t>73.42</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73.29</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>72.97</t>
+          <t>72.79</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>72.70</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>72.47</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72.26</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>72.07</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>71.55</t>
+          <t>71.42</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>71.34</t>
+          <t>71.23</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>71.15</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>70.95</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70.56</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>70.47</t>
+          <t>70.43</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4066,7 +4066,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>70.34</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>70.33</t>
+          <t>70.31</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>70.24</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>70.19</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>70.09</t>
+          <t>70.12</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>69.99</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4336,7 +4336,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>69.78</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>69.75</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>69.76</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>69.64</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>69.59</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>69.54</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>69.47</t>
+          <t>69.56</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>69.39</t>
+          <t>69.50</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>69.31</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>69.27</t>
+          <t>69.40</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>69.36</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>69.20</t>
+          <t>69.31</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>69.27</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>69.21</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>69.00</t>
+          <t>69.15</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>68.96</t>
+          <t>69.11</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>68.93</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>68.90</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>68.85</t>
+          <t>69.00</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>68.79</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4984,7 +4984,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>68.70</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>68.60</t>
+          <t>68.76</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.71</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>68.50</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>68.44</t>
+          <t>68.60</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.53</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>68.32</t>
+          <t>68.48</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>68.43</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>68.22</t>
+          <t>68.38</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>68.27</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>68.04</t>
+          <t>68.20</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>68.13</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>67.90</t>
+          <t>68.06</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -5416,7 +5416,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>67.62</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>67.55</t>
+          <t>67.71</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>67.48</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>67.41</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>67.34</t>
+          <t>67.50</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>67.27</t>
+          <t>67.43</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -5632,7 +5632,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>67.20</t>
+          <t>67.36</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>99.940</t>
+          <t>100.290</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.090</t>
+          <t>100.460</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>102.080</t>
+          <t>102.380</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>103.230</t>
+          <t>103.300</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5816,7 +5816,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107.230</t>
+          <t>107.380</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>109.230</t>
+          <t>109.410</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>109.530</t>
+          <t>109.490</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>107.820</t>
+          <t>107.740</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>87.460</t>
+          <t>87.500</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82.290</t>
+          <t>82.470</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>77.960</t>
+          <t>78.020</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>77.500</t>
+          <t>77.770</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>78.500</t>
+          <t>78.760</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79.740</t>
+          <t>79.700</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>79.700</t>
+          <t>79.820</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>82.600</t>
+          <t>82.720</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>83.790</t>
+          <t>83.910</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>85.340</t>
+          <t>85.590</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>85.480</t>
+          <t>85.730</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>79.270</t>
+          <t>79.530</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>69.560</t>
+          <t>69.750</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64.140</t>
+          <t>64.330</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>62.790</t>
+          <t>62.980</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -6356,7 +6356,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>61.470</t>
+          <t>61.560</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>61.150</t>
+          <t>61.240</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>62.690</t>
+          <t>62.760</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>68.230</t>
+          <t>68.250</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70.500</t>
+          <t>70.520</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>72.490</t>
+          <t>72.510</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>74.760</t>
+          <t>74.970</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>74.350</t>
+          <t>74.560</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -6572,7 +6572,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>71.500</t>
+          <t>71.710</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>61.470</t>
+          <t>61.550</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>57.080</t>
+          <t>57.160</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>55.740</t>
+          <t>55.810</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -6680,7 +6680,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>56.320</t>
+          <t>56.360</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>56.430</t>
+          <t>56.470</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -6734,7 +6734,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>58.090</t>
+          <t>58.130</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>63.150</t>
+          <t>63.200</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>65.270</t>
+          <t>65.170</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>67.140</t>
+          <t>67.040</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>68.210</t>
+          <t>68.110</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>69.210</t>
+          <t>69.110</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>68.220</t>
+          <t>68.110</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>63.370</t>
+          <t>62.970</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -6950,7 +6950,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>60.580</t>
+          <t>60.180</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>57.980</t>
+          <t>57.580</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>55.650</t>
+          <t>55.250</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>54.280</t>
+          <t>53.860</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>55.280</t>
+          <t>54.860</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>63.890</t>
+          <t>63.490</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>66.470</t>
+          <t>66.060</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>68.370</t>
+          <t>67.960</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>69.330</t>
+          <t>69.000</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>69.660</t>
+          <t>69.320</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>68.150</t>
+          <t>67.810</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>63.440</t>
+          <t>63.200</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>59.340</t>
+          <t>59.100</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>56.740</t>
+          <t>56.500</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>55.310</t>
+          <t>55.070</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>54.600</t>
+          <t>54.360</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>55.620</t>
+          <t>55.380</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>60.940</t>
+          <t>60.690</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>63.600</t>
+          <t>63.360</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>66.160</t>
+          <t>65.920</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>15.315</t>
+          <t>15.740</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14.930</t>
+          <t>15.310</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>14.660</t>
+          <t>14.990</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -7647,7 +7647,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14.470</t>
+          <t>14.775</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>14.505</t>
+          <t>14.855</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -7701,7 +7701,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14.385</t>
+          <t>14.735</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>14.115</t>
+          <t>14.400</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -7755,7 +7755,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13.150</t>
+          <t>13.450</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7782,7 +7782,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>11.940</t>
+          <t>12.015</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -7809,7 +7809,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11.380</t>
+          <t>11.480</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>11.415</t>
+          <t>11.465</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -7863,7 +7863,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11.575</t>
+          <t>11.655</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>11.625</t>
+          <t>11.715</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11.720</t>
+          <t>11.820</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>11.670</t>
+          <t>11.735</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11.655</t>
+          <t>11.735</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>11.980</t>
+          <t>12.020</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -8025,7 +8025,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11.975</t>
+          <t>12.035</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>11.780</t>
+          <t>11.845</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10.955</t>
+          <t>11.025</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>9.940</t>
+          <t>9.995</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9.515</t>
+          <t>9.570</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>9.475</t>
+          <t>9.530</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -8187,7 +8187,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9.495</t>
+          <t>9.520</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>9.435</t>
+          <t>9.460</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -8241,7 +8241,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9.470</t>
+          <t>9.495</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>9.400</t>
+          <t>9.390</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -8295,7 +8295,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9.525</t>
+          <t>9.515</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>9.785</t>
+          <t>9.770</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10.805</t>
+          <t>10.680</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>10.630</t>
+          <t>10.510</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>9.885</t>
+          <t>9.780</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>8.970</t>
+          <t>8.870</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -8457,7 +8457,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8.585</t>
+          <t>8.490</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>8.550</t>
+          <t>8.455</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8.570</t>
+          <t>8.445</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>8.515</t>
+          <t>8.395</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>8.550</t>
+          <t>8.425</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>8.485</t>
+          <t>8.335</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>8.595</t>
+          <t>8.440</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>8.830</t>
+          <t>8.670</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>10.180</t>
+          <t>10.010</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>10.015</t>
+          <t>9.850</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -8727,7 +8727,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>9.310</t>
+          <t>9.170</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>8.450</t>
+          <t>8.315</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -8781,7 +8781,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>8.090</t>
+          <t>7.960</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>8.055</t>
+          <t>7.925</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>8.070</t>
+          <t>7.915</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>8.020</t>
+          <t>7.870</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -8889,7 +8889,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>8.050</t>
+          <t>7.895</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>7.990</t>
+          <t>7.810</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -8943,7 +8943,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>8.100</t>
+          <t>7.915</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>8.320</t>
+          <t>8.125</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8997,7 +8997,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>9.550</t>
+          <t>9.345</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>9.395</t>
+          <t>9.195</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>8.740</t>
+          <t>8.555</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>7.930</t>
+          <t>7.760</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9105,7 +9105,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>7.590</t>
+          <t>7.430</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>7.555</t>
+          <t>7.395</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9159,7 +9159,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>7.575</t>
+          <t>7.390</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>7.525</t>
+          <t>7.340</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>7.555</t>
+          <t>7.370</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>7.500</t>
+          <t>7.290</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>7.600</t>
+          <t>7.385</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>7.805</t>
+          <t>7.585</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -9370,7 +9370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>41.480</t>
+          <t>42.014</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>41.635</t>
+          <t>42.159</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40.819</t>
+          <t>42.385</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>40.772</t>
+          <t>42.329</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -9478,7 +9478,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.587</t>
+          <t>42.096</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>40.586</t>
+          <t>42.052</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.407</t>
+          <t>41.792</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>39.992</t>
+          <t>41.228</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -9586,7 +9586,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38.382</t>
+          <t>39.567</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>34.162</t>
+          <t>34.776</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -9640,7 +9640,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32.495</t>
+          <t>32.996</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>32.039</t>
+          <t>32.531</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -9694,7 +9694,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31.981</t>
+          <t>32.446</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>32.016</t>
+          <t>32.501</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32.171</t>
+          <t>32.691</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>31.971</t>
+          <t>32.366</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -9802,7 +9802,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32.031</t>
+          <t>32.401</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>32.436</t>
+          <t>32.831</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -9856,7 +9856,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32.327</t>
+          <t>32.710</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>31.870</t>
+          <t>32.250</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30.227</t>
+          <t>30.610</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>27.107</t>
+          <t>27.430</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -9964,7 +9964,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25.917</t>
+          <t>26.225</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>25.617</t>
+          <t>25.925</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -10018,7 +10018,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25.649</t>
+          <t>25.865</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>25.519</t>
+          <t>25.735</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -10072,7 +10072,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>25.664</t>
+          <t>25.875</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>25.789</t>
+          <t>25.910</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -10126,7 +10126,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26.266</t>
+          <t>26.380</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>26.691</t>
+          <t>26.800</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -10180,7 +10180,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>26.991</t>
+          <t>27.276</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>27.211</t>
+          <t>27.496</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -10234,7 +10234,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>26.541</t>
+          <t>26.821</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>23.285</t>
+          <t>23.531</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -10288,7 +10288,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>22.770</t>
+          <t>23.011</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>22.320</t>
+          <t>22.576</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -10342,7 +10342,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>22.020</t>
+          <t>22.051</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>22.130</t>
+          <t>22.146</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>22.630</t>
+          <t>22.646</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>22.628</t>
+          <t>22.767</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>23.033</t>
+          <t>23.167</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -10477,7 +10477,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>23.418</t>
+          <t>23.547</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -10504,7 +10504,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>23.664</t>
+          <t>23.757</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>23.624</t>
+          <t>23.715</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -10558,7 +10558,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>23.589</t>
+          <t>23.684</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>21.824</t>
+          <t>21.858</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>21.409</t>
+          <t>21.443</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>20.959</t>
+          <t>20.988</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -10666,7 +10666,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>19.954</t>
+          <t>19.983</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10693,7 +10693,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>20.319</t>
+          <t>20.343</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -10720,7 +10720,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>20.984</t>
+          <t>21.003</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10747,7 +10747,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>21.932</t>
+          <t>21.792</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -10774,7 +10774,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>22.707</t>
+          <t>22.560</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>23.142</t>
+          <t>22.993</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -10828,7 +10828,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>23.067</t>
+          <t>23.052</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>22.867</t>
+          <t>22.847</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>22.617</t>
+          <t>22.597</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>21.602</t>
+          <t>21.912</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>21.127</t>
+          <t>21.437</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>20.872</t>
+          <t>21.182</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>20.558</t>
+          <t>20.417</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>20.743</t>
+          <t>20.602</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>21.233</t>
+          <t>21.092</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>22.528</t>
+          <t>22.382</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -11098,7 +11098,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>23.223</t>
+          <t>23.077</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>23.608</t>
+          <t>23.462</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -11152,7 +11152,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>22.973</t>
+          <t>22.892</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>22.833</t>
+          <t>22.752</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>22.733</t>
+          <t>22.652</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>22.953</t>
+          <t>22.872</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>22.633</t>
+          <t>22.552</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>22.083</t>
+          <t>21.997</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>21.733</t>
+          <t>21.647</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>22.178</t>
+          <t>22.092</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>22.713</t>
+          <t>22.627</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>23.508</t>
+          <t>23.422</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>23.863</t>
+          <t>23.777</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>24.038</t>
+          <t>23.952</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -11476,7 +11476,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>24.683</t>
+          <t>24.907</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>24.573</t>
+          <t>24.797</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -11530,7 +11530,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>24.388</t>
+          <t>24.612</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>24.043</t>
+          <t>24.267</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -11584,7 +11584,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>23.588</t>
+          <t>23.812</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -11611,7 +11611,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>23.233</t>
+          <t>23.457</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -11638,7 +11638,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>22.958</t>
+          <t>23.182</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>23.408</t>
+          <t>23.632</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -11692,7 +11692,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>23.803</t>
+          <t>24.027</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>24.403</t>
+          <t>24.626</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -11746,7 +11746,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>24.903</t>
+          <t>25.126</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>25.078</t>
+          <t>25.301</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>26.028</t>
+          <t>26.251</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>25.933</t>
+          <t>26.156</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>25.753</t>
+          <t>25.976</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>25.603</t>
+          <t>25.826</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>25.103</t>
+          <t>25.326</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>24.803</t>
+          <t>25.026</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>24.603</t>
+          <t>24.826</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>25.003</t>
+          <t>25.226</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -12016,7 +12016,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>25.398</t>
+          <t>25.621</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>25.998</t>
+          <t>26.221</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>3.289</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.218</t>
+          <t>3.332</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.175</t>
+          <t>3.285</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.208</t>
+          <t>3.317</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>3.501</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>3.994</t>
+          <t>4.084</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.393</t>
+          <t>4.484</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3.975</t>
+          <t>4.058</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>3.233</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2.957</t>
+          <t>2.996</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.936</t>
+          <t>2.965</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.066</t>
+          <t>3.097</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.281</t>
+          <t>3.303</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3.332</t>
+          <t>3.357</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3.305</t>
+          <t>3.333</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.385</t>
+          <t>3.406</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3.636</t>
+          <t>3.665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.287</t>
+          <t>4.307</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.700</t>
+          <t>4.730</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4.229</t>
+          <t>4.245</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3.443</t>
+          <t>3.454</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3.157</t>
+          <t>3.169</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>3.147</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3.276</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3.488</t>
+          <t>3.504</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3.549</t>
+          <t>3.564</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3.529</t>
+          <t>3.544</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3.595</t>
+          <t>3.609</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3.807</t>
+          <t>3.823</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4.399</t>
+          <t>4.415</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4.802</t>
+          <t>4.813</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>4.333</t>
+          <t>4.345</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.455</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3.126</t>
+          <t>3.132</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3.098</t>
+          <t>3.107</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3.209</t>
+          <t>3.216</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3.421</t>
+          <t>3.429</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3.485</t>
+          <t>3.492</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3.471</t>
+          <t>3.478</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.547</t>
+          <t>3.553</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>3.724</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>4.296</t>
+          <t>4.304</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4.718</t>
+          <t>4.731</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4.263</t>
+          <t>4.276</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3.446</t>
+          <t>3.458</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3.043</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2.987</t>
+          <t>3.001</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>3.109</t>
+          <t>3.124</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3.342</t>
+          <t>3.357</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3.382</t>
+          <t>3.397</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.367</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3.426</t>
+          <t>3.444</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3.625</t>
+          <t>3.643</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>4.155</t>
+          <t>4.172</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -1965,7 +1965,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>4.531</t>
+          <t>4.555</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>4.075</t>
+          <t>4.096</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3.352</t>
+          <t>3.371</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2.944</t>
+          <t>2.964</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2073,7 +2073,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.911</t>
+          <t>2.931</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3.040</t>
+          <t>3.059</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3.242</t>
+          <t>3.261</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>3.319</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>3.279</t>
+          <t>3.299</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3.357</t>
+          <t>3.377</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3.595</t>
+          <t>3.615</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>4.179</t>
+          <t>4.199</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4.505</t>
+          <t>4.525</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>4.042</t>
+          <t>4.062</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>3.283</t>
+          <t>3.303</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>2.828</t>
+          <t>2.848</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2.798</t>
+          <t>2.817</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>2.933</t>
+          <t>2.952</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>3.115</t>
+          <t>3.133</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3.168</t>
+          <t>3.186</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>3.143</t>
+          <t>3.161</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>3.208</t>
+          <t>3.225</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3.423</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>3.948</t>
+          <t>3.964</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4.253</t>
+          <t>4.274</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3.796</t>
+          <t>3.816</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>3.092</t>
+          <t>3.107</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2.731</t>
+          <t>2.748</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2.719</t>
+          <t>2.736</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>2.860</t>
+          <t>2.877</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>3.049</t>
+          <t>3.066</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3.100</t>
+          <t>3.117</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>3.074</t>
+          <t>3.091</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3.147</t>
+          <t>3.164</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>3.386</t>
+          <t>3.403</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3.805</t>
+          <t>3.822</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>4.085</t>
+          <t>4.102</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>3.797</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>3.187</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>2.767</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3045,7 +3045,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>2.757</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>2.890</t>
+          <t>2.907</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.087</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>3.147</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>3.145</t>
+          <t>3.162</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>3.191</t>
+          <t>3.208</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>73.74</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>76.80</t>
+          <t>73.87</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>76.39</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.94</t>
+          <t>73.37</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75.48</t>
+          <t>73.06</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.02</t>
+          <t>72.72</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74.57</t>
+          <t>72.38</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>74.15</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>73.77</t>
+          <t>71.78</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>73.42</t>
+          <t>71.52</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>71.27</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>72.79</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>70.87</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>70.34</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>71.56</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>71.42</t>
+          <t>70.14</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>70.10</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>71.23</t>
+          <t>70.06</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>71.15</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>70.96</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>69.90</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>69.80</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>69.76</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>69.74</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>70.43</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4066,7 +4066,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>70.34</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>70.31</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>69.73</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>69.74</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>70.19</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>70.12</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>69.64</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>69.99</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>69.59</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4336,7 +4336,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.56</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>69.51</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>69.75</t>
+          <t>69.51</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>69.76</t>
+          <t>69.55</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>69.59</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>69.65</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>69.63</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>69.61</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>69.58</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>69.56</t>
+          <t>69.55</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>69.50</t>
+          <t>69.52</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>69.47</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>69.45</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>69.36</t>
+          <t>69.43</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>69.31</t>
+          <t>69.40</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>69.27</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>69.21</t>
+          <t>69.34</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>69.15</t>
+          <t>69.30</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>69.11</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>69.27</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>69.26</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>69.00</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>69.20</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4984,7 +4984,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>69.11</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>69.11</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>68.76</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>68.71</t>
+          <t>69.01</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>68.60</t>
+          <t>68.90</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>68.53</t>
+          <t>68.83</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>68.48</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>68.43</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>68.38</t>
+          <t>68.68</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>68.20</t>
+          <t>68.50</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>68.13</t>
+          <t>68.43</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>68.06</t>
+          <t>68.36</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>68.29</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -5416,7 +5416,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>68.22</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>68.15</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>68.08</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>67.71</t>
+          <t>68.01</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>67.94</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>67.87</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>67.50</t>
+          <t>67.80</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>67.43</t>
+          <t>67.73</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -5632,7 +5632,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>67.36</t>
+          <t>67.66</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>100.290</t>
+          <t>97.180</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.460</t>
+          <t>97.520</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>102.380</t>
+          <t>99.540</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>103.300</t>
+          <t>100.750</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5816,7 +5816,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107.380</t>
+          <t>104.650</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>109.410</t>
+          <t>106.750</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>109.490</t>
+          <t>107.100</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>107.740</t>
+          <t>105.180</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>99.290</t>
+          <t>97.140</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>87.500</t>
+          <t>85.890</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82.470</t>
+          <t>80.810</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>78.020</t>
+          <t>76.940</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>77.770</t>
+          <t>76.530</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>78.760</t>
+          <t>77.490</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79.700</t>
+          <t>78.090</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>79.820</t>
+          <t>78.450</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>82.720</t>
+          <t>81.590</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>83.910</t>
+          <t>82.670</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>85.590</t>
+          <t>84.650</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>85.730</t>
+          <t>84.470</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>79.530</t>
+          <t>78.460</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>69.750</t>
+          <t>69.260</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64.330</t>
+          <t>63.830</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>62.980</t>
+          <t>62.490</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -6356,7 +6356,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>61.560</t>
+          <t>61.060</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>61.240</t>
+          <t>60.740</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>62.760</t>
+          <t>62.250</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>68.250</t>
+          <t>67.880</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70.520</t>
+          <t>70.160</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>72.510</t>
+          <t>72.150</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>74.970</t>
+          <t>74.530</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>74.560</t>
+          <t>74.120</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -6572,7 +6572,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>71.710</t>
+          <t>71.190</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>61.550</t>
+          <t>61.090</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>57.160</t>
+          <t>56.700</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>55.810</t>
+          <t>55.340</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -6680,7 +6680,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>56.360</t>
+          <t>55.990</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>56.470</t>
+          <t>56.100</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -6734,7 +6734,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>58.130</t>
+          <t>57.760</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>63.200</t>
+          <t>62.770</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>65.170</t>
+          <t>64.740</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>67.040</t>
+          <t>66.610</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>68.110</t>
+          <t>67.770</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>69.110</t>
+          <t>68.770</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>68.110</t>
+          <t>67.760</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>62.970</t>
+          <t>62.670</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -6950,7 +6950,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>60.180</t>
+          <t>59.870</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>57.580</t>
+          <t>57.270</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>55.250</t>
+          <t>54.940</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>53.860</t>
+          <t>53.550</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>54.860</t>
+          <t>54.550</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>63.490</t>
+          <t>63.190</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>66.060</t>
+          <t>65.770</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>67.960</t>
+          <t>67.670</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>69.000</t>
+          <t>68.700</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>69.320</t>
+          <t>69.030</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>67.810</t>
+          <t>67.520</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>63.200</t>
+          <t>62.910</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>59.100</t>
+          <t>58.810</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>56.500</t>
+          <t>56.210</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>55.070</t>
+          <t>54.780</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>54.360</t>
+          <t>54.070</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>55.380</t>
+          <t>55.090</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>60.690</t>
+          <t>60.400</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>63.360</t>
+          <t>63.070</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>65.920</t>
+          <t>65.630</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>15.740</t>
+          <t>15.550</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15.310</t>
+          <t>14.845</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>14.990</t>
+          <t>14.550</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -7647,7 +7647,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14.775</t>
+          <t>14.405</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>14.855</t>
+          <t>14.490</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -7701,7 +7701,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14.735</t>
+          <t>14.350</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>14.400</t>
+          <t>14.015</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -7755,7 +7755,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13.450</t>
+          <t>13.130</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7782,7 +7782,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>12.015</t>
+          <t>11.790</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -7809,7 +7809,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11.480</t>
+          <t>11.310</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>11.465</t>
+          <t>11.310</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -7863,7 +7863,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11.655</t>
+          <t>11.490</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>11.715</t>
+          <t>11.530</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11.820</t>
+          <t>11.605</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>11.735</t>
+          <t>11.530</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11.735</t>
+          <t>11.535</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>12.020</t>
+          <t>11.810</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -8025,7 +8025,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12.035</t>
+          <t>11.865</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>11.845</t>
+          <t>11.640</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11.025</t>
+          <t>10.855</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>9.995</t>
+          <t>9.935</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9.570</t>
+          <t>9.510</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>9.530</t>
+          <t>9.470</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -8187,7 +8187,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9.520</t>
+          <t>9.465</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>9.460</t>
+          <t>9.405</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -8241,7 +8241,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9.495</t>
+          <t>9.440</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>9.390</t>
+          <t>9.360</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -8295,7 +8295,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9.515</t>
+          <t>9.480</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>9.770</t>
+          <t>9.735</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10.680</t>
+          <t>10.605</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>10.510</t>
+          <t>10.405</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>9.780</t>
+          <t>9.705</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>8.870</t>
+          <t>8.885</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -8457,7 +8457,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8.490</t>
+          <t>8.500</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>8.455</t>
+          <t>8.465</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8.445</t>
+          <t>8.460</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>8.395</t>
+          <t>8.410</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>8.425</t>
+          <t>8.440</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>8.335</t>
+          <t>8.365</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>8.440</t>
+          <t>8.475</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>8.670</t>
+          <t>8.705</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>10.010</t>
+          <t>9.945</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>9.850</t>
+          <t>9.760</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -8727,7 +8727,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>9.170</t>
+          <t>9.100</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>8.315</t>
+          <t>8.330</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -8781,7 +8781,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>7.960</t>
+          <t>7.975</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>7.925</t>
+          <t>7.940</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>7.915</t>
+          <t>7.935</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>7.870</t>
+          <t>7.885</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -8889,7 +8889,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>7.895</t>
+          <t>7.915</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>7.810</t>
+          <t>7.845</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -8943,7 +8943,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>7.915</t>
+          <t>7.950</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>8.125</t>
+          <t>8.160</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8997,7 +8997,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>9.345</t>
+          <t>9.285</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>9.195</t>
+          <t>9.110</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>8.555</t>
+          <t>8.495</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>7.760</t>
+          <t>7.780</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9105,7 +9105,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>7.430</t>
+          <t>7.445</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>7.395</t>
+          <t>7.415</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9159,7 +9159,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>7.390</t>
+          <t>7.410</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>7.340</t>
+          <t>7.360</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>7.370</t>
+          <t>7.390</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>7.290</t>
+          <t>7.325</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>7.385</t>
+          <t>7.420</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>7.585</t>
+          <t>7.620</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -9370,7 +9370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>42.014</t>
+          <t>40.876</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>42.159</t>
+          <t>41.028</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42.385</t>
+          <t>41.244</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>42.329</t>
+          <t>41.247</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -9478,7 +9478,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.096</t>
+          <t>41.037</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>42.052</t>
+          <t>41.008</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41.792</t>
+          <t>40.795</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>41.228</t>
+          <t>40.240</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -9586,7 +9586,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39.567</t>
+          <t>38.695</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>34.776</t>
+          <t>34.110</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -9640,7 +9640,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32.996</t>
+          <t>32.473</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>32.531</t>
+          <t>32.063</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -9694,7 +9694,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32.446</t>
+          <t>31.991</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>32.501</t>
+          <t>31.995</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32.691</t>
+          <t>32.099</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>32.366</t>
+          <t>31.859</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -9802,7 +9802,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32.401</t>
+          <t>31.909</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>32.831</t>
+          <t>32.309</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -9856,7 +9856,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32.710</t>
+          <t>32.249</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>32.250</t>
+          <t>31.704</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30.610</t>
+          <t>30.154</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>27.430</t>
+          <t>27.285</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -9964,7 +9964,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26.225</t>
+          <t>26.077</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>25.925</t>
+          <t>25.784</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -10018,7 +10018,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25.865</t>
+          <t>25.733</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>25.735</t>
+          <t>25.603</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -10072,7 +10072,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>25.875</t>
+          <t>25.748</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>25.910</t>
+          <t>25.843</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -10126,7 +10126,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26.380</t>
+          <t>26.312</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>26.800</t>
+          <t>26.727</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -10180,7 +10180,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>27.276</t>
+          <t>27.172</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>27.496</t>
+          <t>27.392</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -10234,7 +10234,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>26.821</t>
+          <t>26.717</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>23.531</t>
+          <t>23.498</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -10288,7 +10288,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>23.011</t>
+          <t>22.978</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>22.576</t>
+          <t>22.539</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -10342,7 +10342,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>22.051</t>
+          <t>22.054</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>22.146</t>
+          <t>22.149</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>22.646</t>
+          <t>22.649</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>22.767</t>
+          <t>22.731</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>23.167</t>
+          <t>23.129</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -10477,7 +10477,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>23.547</t>
+          <t>23.507</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -10504,7 +10504,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>23.757</t>
+          <t>23.762</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>23.715</t>
+          <t>23.720</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -10558,7 +10558,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>21.858</t>
+          <t>21.850</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>21.443</t>
+          <t>21.430</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>20.988</t>
+          <t>20.975</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -10666,7 +10666,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>19.983</t>
+          <t>19.970</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10693,7 +10693,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>20.343</t>
+          <t>20.330</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -10720,7 +10720,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>21.003</t>
+          <t>20.990</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10747,7 +10747,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>21.792</t>
+          <t>21.780</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -10774,7 +10774,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>22.560</t>
+          <t>22.550</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>22.993</t>
+          <t>22.980</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -10828,7 +10828,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>23.052</t>
+          <t>23.025</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>22.847</t>
+          <t>22.826</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>22.597</t>
+          <t>22.576</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>21.912</t>
+          <t>21.909</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>21.437</t>
+          <t>21.434</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>21.182</t>
+          <t>21.179</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>20.417</t>
+          <t>20.414</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>20.602</t>
+          <t>20.599</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>21.092</t>
+          <t>21.089</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>22.382</t>
+          <t>22.379</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -11098,7 +11098,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>23.077</t>
+          <t>23.074</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>23.462</t>
+          <t>23.459</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -11152,7 +11152,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>22.892</t>
+          <t>22.879</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>22.752</t>
+          <t>22.739</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>22.652</t>
+          <t>22.639</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>22.872</t>
+          <t>22.859</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>22.552</t>
+          <t>22.539</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>21.997</t>
+          <t>21.984</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>21.647</t>
+          <t>21.634</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>22.092</t>
+          <t>22.079</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>22.627</t>
+          <t>22.614</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>23.422</t>
+          <t>23.409</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>23.777</t>
+          <t>23.764</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>23.952</t>
+          <t>23.939</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -11476,7 +11476,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>24.907</t>
+          <t>24.894</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>24.797</t>
+          <t>24.784</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -11530,7 +11530,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>24.612</t>
+          <t>24.599</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>24.267</t>
+          <t>24.254</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -11584,7 +11584,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>23.812</t>
+          <t>23.799</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -11611,7 +11611,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>23.457</t>
+          <t>23.444</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -11638,7 +11638,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>23.182</t>
+          <t>23.169</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>23.632</t>
+          <t>23.619</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -11692,7 +11692,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>24.027</t>
+          <t>24.014</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>24.626</t>
+          <t>24.614</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -11746,7 +11746,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>25.126</t>
+          <t>25.114</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>25.301</t>
+          <t>25.289</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>26.251</t>
+          <t>26.239</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>26.156</t>
+          <t>26.143</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>25.976</t>
+          <t>25.963</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>25.826</t>
+          <t>25.813</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>25.326</t>
+          <t>25.313</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>25.026</t>
+          <t>25.013</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>24.826</t>
+          <t>24.813</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>25.226</t>
+          <t>25.213</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -12016,7 +12016,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>25.621</t>
+          <t>25.608</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>26.221</t>
+          <t>26.208</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3.289</t>
+          <t>3.398</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.332</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.285</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.501</t>
+          <t>3.498</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4.084</t>
+          <t>4.075</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.484</t>
+          <t>4.472</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4.058</t>
+          <t>4.049</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.233</t>
+          <t>3.234</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2.996</t>
+          <t>3.002</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.965</t>
+          <t>2.973</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.097</t>
+          <t>3.101</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.303</t>
+          <t>3.310</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3.357</t>
+          <t>3.358</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3.333</t>
+          <t>3.334</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.406</t>
+          <t>3.413</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3.665</t>
+          <t>3.666</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.307</t>
+          <t>4.313</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.730</t>
+          <t>4.728</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4.245</t>
+          <t>4.239</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3.454</t>
+          <t>3.449</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>3.166</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3.147</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.276</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3.504</t>
+          <t>3.487</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3.564</t>
+          <t>3.545</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3.544</t>
+          <t>3.524</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>3.587</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3.823</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4.415</t>
+          <t>4.399</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4.813</t>
+          <t>4.798</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>4.345</t>
+          <t>4.333</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3.455</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3.132</t>
+          <t>3.119</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3.107</t>
+          <t>3.094</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3.216</t>
+          <t>3.205</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3.429</t>
+          <t>3.417</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3.492</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3.478</t>
+          <t>3.465</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.553</t>
+          <t>3.539</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3.724</t>
+          <t>3.709</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>4.304</t>
+          <t>4.292</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4.731</t>
+          <t>4.720</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4.276</t>
+          <t>4.269</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3.458</t>
+          <t>3.443</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3.043</t>
+          <t>3.033</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3.001</t>
+          <t>2.991</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>3.124</t>
+          <t>3.114</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3.357</t>
+          <t>3.347</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3.397</t>
+          <t>3.387</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3.367</t>
+          <t>3.357</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3.444</t>
+          <t>3.431</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3.643</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>4.172</t>
+          <t>4.156</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -1965,7 +1965,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>4.555</t>
+          <t>4.539</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>4.096</t>
+          <t>4.081</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3.371</t>
+          <t>3.355</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2.964</t>
+          <t>2.948</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2073,7 +2073,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.931</t>
+          <t>2.915</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3.059</t>
+          <t>3.043</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3.261</t>
+          <t>3.241</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3.319</t>
+          <t>3.299</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>3.299</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3.377</t>
+          <t>3.358</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3.615</t>
+          <t>3.596</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>4.176</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4.525</t>
+          <t>4.503</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>4.062</t>
+          <t>4.042</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>3.303</t>
+          <t>3.282</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>2.848</t>
+          <t>2.827</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2.817</t>
+          <t>2.796</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>2.952</t>
+          <t>2.931</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>3.133</t>
+          <t>3.112</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3.186</t>
+          <t>3.165</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>3.161</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>3.225</t>
+          <t>3.204</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.419</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>3.964</t>
+          <t>3.943</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4.274</t>
+          <t>4.253</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3.816</t>
+          <t>3.795</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>3.107</t>
+          <t>3.086</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2.748</t>
+          <t>2.727</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2.736</t>
+          <t>2.715</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>2.877</t>
+          <t>2.856</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>3.066</t>
+          <t>3.045</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3.117</t>
+          <t>3.096</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>3.091</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3.164</t>
+          <t>3.143</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>3.403</t>
+          <t>3.382</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3.822</t>
+          <t>3.817</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>4.102</t>
+          <t>4.097</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3.797</t>
+          <t>3.792</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>3.187</t>
+          <t>3.182</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2.767</t>
+          <t>2.762</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3045,7 +3045,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2.757</t>
+          <t>2.752</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>2.907</t>
+          <t>2.902</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>3.087</t>
+          <t>3.082</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>3.147</t>
+          <t>3.142</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>3.162</t>
+          <t>3.157</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>3.208</t>
+          <t>3.203</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>73.74</t>
+          <t>75.26</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>73.87</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>75.27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>73.37</t>
+          <t>74.91</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>74.49</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>72.72</t>
+          <t>74.06</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72.38</t>
+          <t>73.64</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>73.25</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71.78</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>71.52</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71.27</t>
+          <t>72.31</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>72.05</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>71.65</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>71.33</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70.34</t>
+          <t>71.19</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>71.04</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>70.14</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>70.10</t>
+          <t>70.87</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>70.06</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>70.65</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>69.90</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>69.76</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69.74</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4066,7 +4066,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>70.27</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>69.73</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>69.74</t>
+          <t>70.27</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>70.23</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>70.17</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>69.64</t>
+          <t>70.12</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>70.08</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>69.59</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4336,7 +4336,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>69.56</t>
+          <t>69.98</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>69.51</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>69.51</t>
+          <t>69.91</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>69.55</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>69.59</t>
+          <t>69.97</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>69.99</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>69.65</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>69.98</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>69.61</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>69.58</t>
+          <t>69.91</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>69.55</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>69.52</t>
+          <t>69.83</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>69.47</t>
+          <t>69.76</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>69.45</t>
+          <t>69.73</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>69.43</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>69.64</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>69.34</t>
+          <t>69.60</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>69.30</t>
+          <t>69.55</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>69.27</t>
+          <t>69.51</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>69.26</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>69.20</t>
+          <t>69.42</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4984,7 +4984,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>69.11</t>
+          <t>69.34</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>69.11</t>
+          <t>69.32</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>69.01</t>
+          <t>69.24</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>68.96</t>
+          <t>69.20</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>68.90</t>
+          <t>69.15</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>68.83</t>
+          <t>69.09</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>68.78</t>
+          <t>69.04</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>68.99</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>68.68</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>68.50</t>
+          <t>68.79</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>68.43</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>68.36</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>68.29</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -5416,7 +5416,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>68.22</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>68.15</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>68.08</t>
+          <t>68.43</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>68.01</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>67.94</t>
+          <t>68.31</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>67.87</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>67.80</t>
+          <t>68.19</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>67.73</t>
+          <t>68.13</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -5632,7 +5632,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>67.66</t>
+          <t>68.07</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>97.180</t>
+          <t>96.520</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>97.520</t>
+          <t>96.470</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>99.540</t>
+          <t>98.320</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.750</t>
+          <t>99.310</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5816,7 +5816,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104.650</t>
+          <t>103.120</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>106.750</t>
+          <t>105.100</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>107.100</t>
+          <t>105.600</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>105.180</t>
+          <t>103.650</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97.140</t>
+          <t>95.580</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>85.890</t>
+          <t>84.860</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80.810</t>
+          <t>80.300</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>76.940</t>
+          <t>76.170</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>76.530</t>
+          <t>75.820</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>77.490</t>
+          <t>76.730</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>78.090</t>
+          <t>77.370</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>78.450</t>
+          <t>77.590</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81.590</t>
+          <t>80.830</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>82.670</t>
+          <t>81.850</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>84.650</t>
+          <t>83.670</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>84.470</t>
+          <t>83.520</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>78.460</t>
+          <t>77.780</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>69.260</t>
+          <t>68.670</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>63.830</t>
+          <t>63.360</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>62.490</t>
+          <t>62.010</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -6356,7 +6356,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>61.060</t>
+          <t>60.580</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>60.740</t>
+          <t>60.260</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>62.250</t>
+          <t>61.780</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>67.880</t>
+          <t>67.620</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70.160</t>
+          <t>69.900</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>72.150</t>
+          <t>71.890</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>74.530</t>
+          <t>74.250</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>74.120</t>
+          <t>73.840</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -6572,7 +6572,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>71.190</t>
+          <t>70.920</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>61.090</t>
+          <t>60.990</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>56.700</t>
+          <t>56.600</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>55.340</t>
+          <t>55.240</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -6680,7 +6680,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>55.990</t>
+          <t>55.910</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>56.100</t>
+          <t>56.000</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -6734,7 +6734,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>57.760</t>
+          <t>57.650</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>62.770</t>
+          <t>62.740</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>64.740</t>
+          <t>64.710</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>66.610</t>
+          <t>66.580</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>67.770</t>
+          <t>67.510</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>68.770</t>
+          <t>68.510</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>67.760</t>
+          <t>67.500</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>62.670</t>
+          <t>62.330</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -6950,7 +6950,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>59.870</t>
+          <t>59.530</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>57.270</t>
+          <t>56.930</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>54.940</t>
+          <t>54.600</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>53.550</t>
+          <t>53.190</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>54.550</t>
+          <t>54.200</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>63.190</t>
+          <t>62.730</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>65.770</t>
+          <t>65.320</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>67.670</t>
+          <t>67.210</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>68.700</t>
+          <t>68.430</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>69.030</t>
+          <t>68.760</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>67.520</t>
+          <t>67.250</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>62.910</t>
+          <t>62.640</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>58.810</t>
+          <t>58.540</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>56.210</t>
+          <t>55.940</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>54.780</t>
+          <t>54.510</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>54.070</t>
+          <t>53.800</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>55.090</t>
+          <t>54.820</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>60.400</t>
+          <t>60.130</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>63.070</t>
+          <t>62.800</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>65.630</t>
+          <t>65.350</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>15.550</t>
+          <t>15.385</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14.845</t>
+          <t>14.735</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>14.550</t>
+          <t>14.390</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -7647,7 +7647,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14.405</t>
+          <t>14.235</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>14.490</t>
+          <t>14.315</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -7701,7 +7701,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14.350</t>
+          <t>14.200</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>14.015</t>
+          <t>13.875</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -7755,7 +7755,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13.130</t>
+          <t>13.010</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7782,7 +7782,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>11.790</t>
+          <t>11.705</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -7809,7 +7809,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11.310</t>
+          <t>11.235</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>11.310</t>
+          <t>11.295</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -7863,7 +7863,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11.490</t>
+          <t>11.445</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>11.530</t>
+          <t>11.505</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11.605</t>
+          <t>11.520</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>11.530</t>
+          <t>11.480</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11.535</t>
+          <t>11.475</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>11.810</t>
+          <t>11.750</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -8025,7 +8025,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11.865</t>
+          <t>11.820</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>11.640</t>
+          <t>11.605</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10.855</t>
+          <t>10.850</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>9.935</t>
+          <t>9.915</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9.510</t>
+          <t>9.505</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>9.470</t>
+          <t>9.465</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -8187,7 +8187,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9.465</t>
+          <t>9.445</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>9.405</t>
+          <t>9.385</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -8241,7 +8241,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9.440</t>
+          <t>9.425</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8295,7 +8295,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9.480</t>
+          <t>9.485</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10.605</t>
+          <t>10.645</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>10.405</t>
+          <t>10.450</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>9.705</t>
+          <t>9.770</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>8.885</t>
+          <t>8.925</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -8457,7 +8457,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8.500</t>
+          <t>8.560</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>8.465</t>
+          <t>8.525</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8.460</t>
+          <t>8.505</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>8.410</t>
+          <t>8.450</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>8.440</t>
+          <t>8.485</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>8.365</t>
+          <t>8.430</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>8.475</t>
+          <t>8.540</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>8.705</t>
+          <t>8.765</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>9.945</t>
+          <t>9.965</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>9.760</t>
+          <t>9.785</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -8727,7 +8727,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>9.100</t>
+          <t>9.150</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>8.330</t>
+          <t>8.360</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -8781,7 +8781,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>7.975</t>
+          <t>8.015</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>7.940</t>
+          <t>7.980</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>7.935</t>
+          <t>7.965</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>7.885</t>
+          <t>7.915</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -8889,7 +8889,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>7.915</t>
+          <t>7.945</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>7.845</t>
+          <t>7.890</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -8943,7 +8943,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>7.950</t>
+          <t>7.995</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>8.160</t>
+          <t>8.210</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8997,7 +8997,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>9.285</t>
+          <t>9.290</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>9.110</t>
+          <t>9.120</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>8.495</t>
+          <t>8.525</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>7.780</t>
+          <t>7.790</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9105,7 +9105,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>7.445</t>
+          <t>7.470</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>7.415</t>
+          <t>7.440</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9159,7 +9159,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>7.410</t>
+          <t>7.420</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>7.360</t>
+          <t>7.375</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>7.390</t>
+          <t>7.405</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>7.325</t>
+          <t>7.355</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>7.420</t>
+          <t>7.450</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>7.620</t>
+          <t>7.650</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -9370,7 +9370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>40.876</t>
+          <t>40.280</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>41.028</t>
+          <t>40.499</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41.244</t>
+          <t>40.744</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>41.247</t>
+          <t>40.688</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -9478,7 +9478,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41.037</t>
+          <t>40.443</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>41.008</t>
+          <t>40.402</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.795</t>
+          <t>40.224</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>40.240</t>
+          <t>39.702</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -9586,7 +9586,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38.695</t>
+          <t>38.229</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>34.110</t>
+          <t>33.875</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -9640,7 +9640,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32.473</t>
+          <t>32.343</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>32.063</t>
+          <t>31.898</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -9694,7 +9694,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31.991</t>
+          <t>31.858</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>31.995</t>
+          <t>31.848</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32.099</t>
+          <t>31.923</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>31.859</t>
+          <t>31.638</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -9802,7 +9802,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31.909</t>
+          <t>31.791</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>32.309</t>
+          <t>32.121</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -9856,7 +9856,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32.249</t>
+          <t>32.041</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>31.704</t>
+          <t>31.516</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30.154</t>
+          <t>30.072</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>27.285</t>
+          <t>27.154</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -9964,7 +9964,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26.077</t>
+          <t>26.007</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>25.784</t>
+          <t>25.712</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -10018,7 +10018,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25.733</t>
+          <t>25.617</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>25.603</t>
+          <t>25.487</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -10072,7 +10072,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>25.748</t>
+          <t>25.637</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>25.843</t>
+          <t>25.788</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -10126,7 +10126,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26.312</t>
+          <t>26.259</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>26.727</t>
+          <t>26.674</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -10180,7 +10180,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>27.172</t>
+          <t>27.109</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>27.392</t>
+          <t>27.325</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -10234,7 +10234,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>26.717</t>
+          <t>26.654</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>23.498</t>
+          <t>23.525</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -10288,7 +10288,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>22.978</t>
+          <t>23.005</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>22.539</t>
+          <t>22.565</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -10342,7 +10342,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>22.054</t>
+          <t>22.085</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>22.149</t>
+          <t>22.175</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>22.649</t>
+          <t>22.670</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>22.731</t>
+          <t>22.790</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>23.129</t>
+          <t>23.190</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -10477,7 +10477,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>23.507</t>
+          <t>23.565</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -10504,7 +10504,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>23.762</t>
+          <t>23.725</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>23.720</t>
+          <t>23.684</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -10558,7 +10558,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>23.684</t>
+          <t>23.649</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>21.850</t>
+          <t>21.787</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>21.430</t>
+          <t>21.367</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>20.975</t>
+          <t>20.912</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -10666,7 +10666,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>19.970</t>
+          <t>19.907</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10693,7 +10693,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>20.330</t>
+          <t>20.257</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -10720,7 +10720,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>20.990</t>
+          <t>20.922</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10747,7 +10747,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>21.780</t>
+          <t>21.667</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -10774,7 +10774,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>22.550</t>
+          <t>22.442</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>22.980</t>
+          <t>22.867</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -10828,7 +10828,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>23.025</t>
+          <t>23.037</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>22.826</t>
+          <t>22.851</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>22.576</t>
+          <t>22.628</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>21.909</t>
+          <t>21.944</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>21.434</t>
+          <t>21.469</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>21.179</t>
+          <t>21.214</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>20.414</t>
+          <t>20.449</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>20.599</t>
+          <t>20.634</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>21.089</t>
+          <t>21.124</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>22.379</t>
+          <t>22.414</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -11098,7 +11098,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>23.074</t>
+          <t>23.109</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>23.459</t>
+          <t>23.489</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -11152,7 +11152,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>22.879</t>
+          <t>22.979</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>22.739</t>
+          <t>22.839</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>22.639</t>
+          <t>22.739</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>22.859</t>
+          <t>22.909</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>22.539</t>
+          <t>22.589</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>21.984</t>
+          <t>22.034</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>21.634</t>
+          <t>21.684</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>22.079</t>
+          <t>22.129</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>22.614</t>
+          <t>22.664</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>23.409</t>
+          <t>23.459</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>23.764</t>
+          <t>23.814</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>23.939</t>
+          <t>23.989</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -11476,7 +11476,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>24.894</t>
+          <t>24.943</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>24.784</t>
+          <t>24.833</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -11530,7 +11530,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>24.599</t>
+          <t>24.648</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>24.254</t>
+          <t>24.283</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -11584,7 +11584,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>23.799</t>
+          <t>23.828</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -11611,7 +11611,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>23.444</t>
+          <t>23.473</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -11638,7 +11638,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>23.169</t>
+          <t>23.198</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>23.619</t>
+          <t>23.648</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -11692,7 +11692,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>24.014</t>
+          <t>24.043</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>24.614</t>
+          <t>24.643</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -11746,7 +11746,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>25.114</t>
+          <t>25.143</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>25.289</t>
+          <t>25.318</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>26.239</t>
+          <t>26.268</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>26.143</t>
+          <t>26.173</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>25.963</t>
+          <t>25.993</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>25.813</t>
+          <t>25.823</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>25.313</t>
+          <t>25.323</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>25.013</t>
+          <t>25.023</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>24.813</t>
+          <t>24.823</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>25.213</t>
+          <t>25.223</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -12016,7 +12016,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>25.608</t>
+          <t>25.618</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>26.208</t>
+          <t>26.218</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -507,22 +507,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>JUL 26</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>JUL 26</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3.398</t>
+          <t>3.231</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>3.279</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.226</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.317</t>
+          <t>3.255</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.498</t>
+          <t>3.439</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4.075</t>
+          <t>4.028</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.472</t>
+          <t>4.432</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4.049</t>
+          <t>4.005</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.234</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3.002</t>
+          <t>2.973</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.973</t>
+          <t>2.943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.101</t>
+          <t>3.074</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>3.284</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3.358</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3.334</t>
+          <t>3.316</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.413</t>
+          <t>3.393</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3.666</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.313</t>
+          <t>4.296</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.728</t>
+          <t>4.715</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4.239</t>
+          <t>4.232</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3.449</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3.166</t>
+          <t>3.157</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3.276</t>
+          <t>3.265</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3.487</t>
+          <t>3.476</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3.545</t>
+          <t>3.535</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3.524</t>
+          <t>3.515</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3.587</t>
+          <t>3.580</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4.399</t>
+          <t>4.389</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4.798</t>
+          <t>4.788</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>4.333</t>
+          <t>4.323</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3.119</t>
+          <t>3.109</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3.094</t>
+          <t>3.084</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3.205</t>
+          <t>3.195</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3.417</t>
+          <t>3.407</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>3.455</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.539</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3.709</t>
+          <t>3.700</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>4.283</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4.720</t>
+          <t>4.712</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4.269</t>
+          <t>4.262</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3.443</t>
+          <t>3.435</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3.033</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2.991</t>
+          <t>2.984</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>3.114</t>
+          <t>3.107</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3.347</t>
+          <t>3.341</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3.387</t>
+          <t>3.381</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3.357</t>
+          <t>3.351</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3.431</t>
+          <t>3.425</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>3.625</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>4.156</t>
+          <t>4.153</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -1965,7 +1965,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>4.539</t>
+          <t>4.538</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>4.081</t>
+          <t>4.083</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3.355</t>
+          <t>3.356</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2.948</t>
+          <t>2.951</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2073,7 +2073,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.915</t>
+          <t>2.918</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3.043</t>
+          <t>3.046</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3.241</t>
+          <t>3.246</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3.299</t>
+          <t>3.303</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.285</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3.358</t>
+          <t>3.363</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3.596</t>
+          <t>3.602</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>4.176</t>
+          <t>4.184</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4.503</t>
+          <t>4.510</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>4.042</t>
+          <t>4.049</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>3.282</t>
+          <t>3.289</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>2.827</t>
+          <t>2.834</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2.796</t>
+          <t>2.803</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>2.931</t>
+          <t>2.938</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>3.112</t>
+          <t>3.119</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3.165</t>
+          <t>3.172</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>3.147</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>3.204</t>
+          <t>3.211</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3.419</t>
+          <t>3.426</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>3.943</t>
+          <t>3.950</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4.253</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3.795</t>
+          <t>3.802</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>3.086</t>
+          <t>3.093</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2.727</t>
+          <t>2.734</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2.715</t>
+          <t>2.722</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>2.856</t>
+          <t>2.863</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>3.045</t>
+          <t>3.052</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3.096</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.077</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3.143</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>3.382</t>
+          <t>3.389</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3.817</t>
+          <t>3.824</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>4.097</t>
+          <t>4.104</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3.792</t>
+          <t>3.799</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>3.182</t>
+          <t>3.189</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2.762</t>
+          <t>2.769</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3045,7 +3045,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2.752</t>
+          <t>2.759</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>2.902</t>
+          <t>2.909</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>3.082</t>
+          <t>3.089</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>3.142</t>
+          <t>3.149</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>3.157</t>
+          <t>3.164</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>3.203</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>71.99</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75.27</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>74.91</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>74.06</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>73.64</t>
+          <t>71.57</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>73.25</t>
+          <t>71.30</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>70.85</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>70.65</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>72.05</t>
+          <t>70.47</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>71.65</t>
+          <t>70.19</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>71.48</t>
+          <t>70.07</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>71.33</t>
+          <t>69.97</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71.19</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>71.04</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>69.71</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>69.64</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>69.59</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70.46</t>
+          <t>69.58</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>69.58</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>70.30</t>
+          <t>69.56</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4066,7 +4066,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>70.27</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>70.27</t>
+          <t>69.74</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>69.74</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>69.71</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>70.12</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>70.08</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4336,7 +4336,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>69.98</t>
+          <t>69.65</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>69.61</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>69.91</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>69.97</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>69.99</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>69.81</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>69.98</t>
+          <t>69.81</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>69.80</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>69.91</t>
+          <t>69.78</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>69.76</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>69.83</t>
+          <t>69.75</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>69.76</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>69.73</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>69.64</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>69.60</t>
+          <t>69.65</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>69.55</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>69.51</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>69.61</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>69.42</t>
+          <t>69.59</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4984,7 +4984,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>69.34</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>69.32</t>
+          <t>69.52</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>69.51</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>69.24</t>
+          <t>69.50</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>69.20</t>
+          <t>69.48</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>69.15</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>69.09</t>
+          <t>69.43</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>69.04</t>
+          <t>69.40</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>69.37</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>69.34</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>68.89</t>
+          <t>69.31</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>68.79</t>
+          <t>69.25</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>69.18</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>69.11</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>69.04</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -5416,7 +5416,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.97</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>68.90</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>68.43</t>
+          <t>68.83</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.76</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>68.31</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>68.19</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>68.13</t>
+          <t>68.48</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -5632,7 +5632,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>68.07</t>
+          <t>68.41</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>96.520</t>
+          <t>97.800</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>96.470</t>
+          <t>97.800</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98.320</t>
+          <t>99.530</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>99.310</t>
+          <t>100.450</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5816,7 +5816,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103.120</t>
+          <t>104.110</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>105.100</t>
+          <t>106.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>105.600</t>
+          <t>106.410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>103.650</t>
+          <t>104.460</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95.580</t>
+          <t>96.390</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>84.860</t>
+          <t>85.030</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80.300</t>
+          <t>80.470</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>76.170</t>
+          <t>76.340</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75.820</t>
+          <t>75.850</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>76.730</t>
+          <t>76.740</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77.370</t>
+          <t>77.270</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>77.590</t>
+          <t>77.310</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>80.830</t>
+          <t>80.650</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>81.850</t>
+          <t>81.670</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>83.670</t>
+          <t>83.490</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>83.520</t>
+          <t>83.340</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>77.780</t>
+          <t>77.600</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>68.670</t>
+          <t>69.290</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>63.360</t>
+          <t>63.980</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>62.010</t>
+          <t>62.630</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -6356,7 +6356,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>60.580</t>
+          <t>61.200</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>60.260</t>
+          <t>60.880</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>61.780</t>
+          <t>62.400</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>67.620</t>
+          <t>67.840</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69.900</t>
+          <t>70.120</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>71.890</t>
+          <t>72.110</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>74.250</t>
+          <t>74.470</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>73.840</t>
+          <t>74.060</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -6572,7 +6572,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>70.920</t>
+          <t>71.140</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>60.990</t>
+          <t>61.210</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>56.600</t>
+          <t>56.820</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>55.240</t>
+          <t>55.460</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -6680,7 +6680,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>55.910</t>
+          <t>56.130</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>56.000</t>
+          <t>56.220</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -6734,7 +6734,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>57.650</t>
+          <t>57.870</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>62.740</t>
+          <t>62.960</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>64.710</t>
+          <t>64.930</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>66.580</t>
+          <t>66.800</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>67.510</t>
+          <t>67.730</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>68.510</t>
+          <t>68.730</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>67.500</t>
+          <t>67.720</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>62.330</t>
+          <t>62.550</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -6950,7 +6950,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>59.530</t>
+          <t>59.760</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>56.930</t>
+          <t>57.160</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>54.600</t>
+          <t>54.830</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>53.190</t>
+          <t>53.420</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>54.200</t>
+          <t>54.430</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>62.730</t>
+          <t>62.960</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>65.320</t>
+          <t>65.550</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>67.210</t>
+          <t>67.440</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>68.430</t>
+          <t>68.660</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>68.760</t>
+          <t>68.990</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>67.250</t>
+          <t>67.480</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>62.640</t>
+          <t>62.870</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>58.540</t>
+          <t>58.770</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>55.940</t>
+          <t>56.170</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>54.510</t>
+          <t>54.740</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>53.800</t>
+          <t>54.030</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>54.820</t>
+          <t>55.050</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>60.130</t>
+          <t>60.360</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>62.800</t>
+          <t>63.030</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>65.350</t>
+          <t>65.580</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>15.385</t>
+          <t>15.525</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14.735</t>
+          <t>14.960</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>14.390</t>
+          <t>14.510</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -7647,7 +7647,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14.235</t>
+          <t>14.330</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>14.315</t>
+          <t>14.400</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -7701,7 +7701,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14.200</t>
+          <t>14.205</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>13.875</t>
+          <t>13.840</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -7755,7 +7755,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13.010</t>
+          <t>12.995</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7782,7 +7782,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>11.705</t>
+          <t>11.675</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -7809,7 +7809,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11.235</t>
+          <t>11.185</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>11.295</t>
+          <t>11.260</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -7863,7 +7863,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11.445</t>
+          <t>11.405</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>11.505</t>
+          <t>11.470</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11.520</t>
+          <t>11.480</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>11.480</t>
+          <t>11.450</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11.475</t>
+          <t>11.435</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>11.750</t>
+          <t>11.740</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -8025,7 +8025,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11.820</t>
+          <t>11.770</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>11.605</t>
+          <t>11.550</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10.850</t>
+          <t>10.795</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>9.915</t>
+          <t>9.860</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9.505</t>
+          <t>9.455</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>9.465</t>
+          <t>9.415</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -8187,7 +8187,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9.445</t>
+          <t>9.390</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>9.385</t>
+          <t>9.330</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -8241,7 +8241,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9.425</t>
+          <t>9.370</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>9.360</t>
+          <t>9.325</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -8295,7 +8295,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9.485</t>
+          <t>9.450</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>9.735</t>
+          <t>9.705</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10.645</t>
+          <t>10.640</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>10.450</t>
+          <t>10.445</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>9.770</t>
+          <t>9.760</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>8.925</t>
+          <t>8.915</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -8457,7 +8457,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8.560</t>
+          <t>8.550</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>8.525</t>
+          <t>8.510</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8.505</t>
+          <t>8.490</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>8.450</t>
+          <t>8.435</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>8.485</t>
+          <t>8.470</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>8.765</t>
+          <t>8.775</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>9.965</t>
+          <t>9.980</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>9.785</t>
+          <t>9.795</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -8727,7 +8727,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>9.150</t>
+          <t>9.155</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8781,7 +8781,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>7.915</t>
+          <t>7.910</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -8889,7 +8889,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>7.890</t>
+          <t>7.905</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -8943,7 +8943,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>7.995</t>
+          <t>8.010</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>8.210</t>
+          <t>8.230</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8997,7 +8997,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>9.290</t>
+          <t>9.320</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>9.120</t>
+          <t>9.145</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>8.525</t>
+          <t>8.550</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>7.790</t>
+          <t>7.805</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9105,7 +9105,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>7.470</t>
+          <t>7.485</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>7.440</t>
+          <t>7.455</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9159,7 +9159,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>7.420</t>
+          <t>7.435</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>7.375</t>
+          <t>7.390</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>7.405</t>
+          <t>7.420</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>7.355</t>
+          <t>7.385</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>7.450</t>
+          <t>7.480</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>7.650</t>
+          <t>7.685</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -9370,7 +9370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>40.280</t>
+          <t>40.782</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.499</t>
+          <t>40.842</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40.744</t>
+          <t>41.087</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>40.688</t>
+          <t>41.068</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -9478,7 +9478,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.443</t>
+          <t>40.728</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>40.402</t>
+          <t>40.683</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.224</t>
+          <t>40.437</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>39.702</t>
+          <t>39.817</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -9586,7 +9586,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38.229</t>
+          <t>38.327</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>33.875</t>
+          <t>33.817</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -9640,7 +9640,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32.343</t>
+          <t>32.184</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>31.898</t>
+          <t>31.779</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -9694,7 +9694,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31.858</t>
+          <t>31.700</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>31.848</t>
+          <t>31.701</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31.923</t>
+          <t>31.766</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>31.638</t>
+          <t>31.461</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -9802,7 +9802,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31.791</t>
+          <t>31.600</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>32.121</t>
+          <t>32.020</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -9856,7 +9856,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32.041</t>
+          <t>31.892</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>31.516</t>
+          <t>31.367</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30.072</t>
+          <t>29.927</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>27.154</t>
+          <t>27.022</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -9964,7 +9964,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26.007</t>
+          <t>25.883</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>25.712</t>
+          <t>25.588</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -10018,7 +10018,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25.617</t>
+          <t>25.491</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>25.487</t>
+          <t>25.361</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -10072,7 +10072,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>25.637</t>
+          <t>25.511</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>25.788</t>
+          <t>25.718</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -10126,7 +10126,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26.259</t>
+          <t>26.188</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>26.674</t>
+          <t>26.607</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -10180,7 +10180,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>27.109</t>
+          <t>27.034</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>27.325</t>
+          <t>27.249</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -10234,7 +10234,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>26.654</t>
+          <t>26.584</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>23.525</t>
+          <t>23.429</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -10288,7 +10288,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>23.005</t>
+          <t>22.909</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>22.565</t>
+          <t>22.474</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -10342,7 +10342,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>22.085</t>
+          <t>21.994</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>22.175</t>
+          <t>22.084</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>22.670</t>
+          <t>22.579</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>22.790</t>
+          <t>22.693</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>23.190</t>
+          <t>23.093</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -10477,7 +10477,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>23.565</t>
+          <t>23.468</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -10504,7 +10504,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>23.725</t>
+          <t>23.688</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>23.684</t>
+          <t>23.643</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -10558,7 +10558,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>23.649</t>
+          <t>23.608</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>21.787</t>
+          <t>21.798</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>21.367</t>
+          <t>21.378</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>20.912</t>
+          <t>20.923</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -10666,7 +10666,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>19.907</t>
+          <t>19.918</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10693,7 +10693,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>20.257</t>
+          <t>20.268</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -10720,7 +10720,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>20.922</t>
+          <t>20.933</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10747,7 +10747,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>21.667</t>
+          <t>21.673</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -10774,7 +10774,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>22.442</t>
+          <t>22.448</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>22.867</t>
+          <t>22.878</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -10828,7 +10828,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>23.037</t>
+          <t>23.118</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>22.851</t>
+          <t>22.928</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>22.628</t>
+          <t>22.703</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>21.944</t>
+          <t>21.980</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>21.469</t>
+          <t>21.505</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>21.214</t>
+          <t>21.250</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>20.449</t>
+          <t>20.485</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>20.634</t>
+          <t>20.670</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>21.124</t>
+          <t>21.160</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>22.414</t>
+          <t>22.450</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -11098,7 +11098,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>23.109</t>
+          <t>23.145</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>23.489</t>
+          <t>23.525</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -11152,7 +11152,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>22.979</t>
+          <t>23.045</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>22.839</t>
+          <t>22.906</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>22.739</t>
+          <t>22.806</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>22.909</t>
+          <t>22.976</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>22.589</t>
+          <t>22.656</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>22.034</t>
+          <t>22.101</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>21.684</t>
+          <t>21.751</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>22.129</t>
+          <t>22.196</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>22.664</t>
+          <t>22.731</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>23.459</t>
+          <t>23.526</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>23.814</t>
+          <t>23.881</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>23.989</t>
+          <t>24.056</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -11476,7 +11476,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>24.943</t>
+          <t>25.011</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>24.833</t>
+          <t>24.901</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -11530,7 +11530,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>24.648</t>
+          <t>24.716</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>24.283</t>
+          <t>24.351</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -11584,7 +11584,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>23.828</t>
+          <t>23.896</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -11611,7 +11611,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>23.473</t>
+          <t>23.541</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -11638,7 +11638,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>23.198</t>
+          <t>23.266</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>23.648</t>
+          <t>23.716</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -11692,7 +11692,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>24.043</t>
+          <t>24.111</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>24.643</t>
+          <t>24.711</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -11746,7 +11746,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>25.143</t>
+          <t>25.211</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>25.318</t>
+          <t>25.386</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>26.268</t>
+          <t>26.336</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>26.173</t>
+          <t>26.241</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>25.993</t>
+          <t>26.061</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>25.823</t>
+          <t>25.891</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>25.323</t>
+          <t>25.391</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>25.023</t>
+          <t>25.091</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>24.823</t>
+          <t>24.891</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>25.223</t>
+          <t>25.291</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -12016,7 +12016,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>25.618</t>
+          <t>25.686</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>26.218</t>
+          <t>26.286</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3.279</t>
+          <t>3.233</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.226</t>
+          <t>3.181</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.255</t>
+          <t>3.209</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.439</t>
+          <t>3.392</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4.028</t>
+          <t>3.987</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.432</t>
+          <t>4.397</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4.005</t>
+          <t>3.968</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>3.161</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2.973</t>
+          <t>2.940</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2.943</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.074</t>
+          <t>3.041</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.284</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>3.306</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3.316</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3.393</t>
+          <t>3.357</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.617</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.296</t>
+          <t>4.272</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4.715</t>
+          <t>4.689</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4.232</t>
+          <t>4.213</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.426</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3.157</t>
+          <t>3.149</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>3.124</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3.265</t>
+          <t>3.261</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3.476</t>
+          <t>3.474</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3.535</t>
+          <t>3.534</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3.515</t>
+          <t>3.512</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>3.576</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>3.786</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4.389</t>
+          <t>4.386</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4.788</t>
+          <t>4.786</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>4.323</t>
+          <t>4.326</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.433</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3.195</t>
+          <t>3.194</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.531</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3.700</t>
+          <t>3.701</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>4.283</t>
+          <t>4.285</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4.712</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4.262</t>
+          <t>4.265</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3.435</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2.984</t>
+          <t>2.985</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>3.107</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3.341</t>
+          <t>3.337</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3.381</t>
+          <t>3.373</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3.351</t>
+          <t>3.346</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3.425</t>
+          <t>3.424</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3.625</t>
+          <t>3.623</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>4.153</t>
+          <t>4.152</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -1965,7 +1965,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>4.538</t>
+          <t>4.537</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3.356</t>
+          <t>3.358</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2.951</t>
+          <t>2.957</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2073,7 +2073,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.918</t>
+          <t>2.924</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3.046</t>
+          <t>3.052</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3.246</t>
+          <t>3.252</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3.303</t>
+          <t>3.309</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>3.285</t>
+          <t>3.291</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3.363</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3.602</t>
+          <t>3.599</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>4.184</t>
+          <t>4.181</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4.510</t>
+          <t>4.507</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>4.049</t>
+          <t>4.034</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>3.289</t>
+          <t>3.274</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>2.834</t>
+          <t>2.819</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2.803</t>
+          <t>2.788</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>2.938</t>
+          <t>2.923</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>3.119</t>
+          <t>3.104</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3.172</t>
+          <t>3.157</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>3.147</t>
+          <t>3.132</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>3.211</t>
+          <t>3.196</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3.426</t>
+          <t>3.411</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>3.935</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>4.247</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3.802</t>
+          <t>3.793</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>3.093</t>
+          <t>3.084</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2.734</t>
+          <t>2.725</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2.722</t>
+          <t>2.713</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>2.863</t>
+          <t>2.862</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>3.052</t>
+          <t>3.051</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.102</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>3.077</t>
+          <t>3.076</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>3.149</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>3.389</t>
+          <t>3.388</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3.824</t>
+          <t>3.823</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>4.104</t>
+          <t>4.103</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3.799</t>
+          <t>3.798</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>3.189</t>
+          <t>3.188</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2.769</t>
+          <t>2.768</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3045,7 +3045,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2.759</t>
+          <t>2.758</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>2.908</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>3.089</t>
+          <t>3.088</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>3.148</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>3.164</t>
+          <t>3.163</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>3.209</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>73.82</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>73.61</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>73.32</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>72.97</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>71.57</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>71.30</t>
+          <t>72.26</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>71.95</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>70.85</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>71.42</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>70.47</t>
+          <t>71.19</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>71.00</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>70.19</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>70.07</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>69.97</t>
+          <t>70.54</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>69.71</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>70.12</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>70.07</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.99</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>69.64</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>69.89</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>69.59</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>69.58</t>
+          <t>69.80</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69.58</t>
+          <t>69.75</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>69.56</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4066,7 +4066,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.74</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>69.76</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>69.74</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>69.74</t>
+          <t>69.76</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.63</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4336,7 +4336,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>69.65</t>
+          <t>69.60</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>69.61</t>
+          <t>69.55</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>69.55</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>69.59</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>69.63</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>69.81</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>69.81</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>69.76</t>
+          <t>69.64</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>69.75</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>69.56</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>69.55</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>69.54</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>69.52</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>69.65</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>69.45</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>69.45</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>69.45</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>69.61</t>
+          <t>69.42</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>69.59</t>
+          <t>69.39</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4984,7 +4984,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>69.33</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>69.52</t>
+          <t>69.31</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>69.51</t>
+          <t>69.29</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>69.50</t>
+          <t>69.27</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>69.24</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>69.21</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>69.43</t>
+          <t>69.17</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>69.13</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>69.37</t>
+          <t>69.09</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>69.34</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>69.31</t>
+          <t>69.01</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>68.97</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>69.25</t>
+          <t>68.93</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>69.18</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>69.11</t>
+          <t>68.79</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>69.04</t>
+          <t>68.72</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -5416,7 +5416,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>68.97</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>68.90</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>68.83</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>68.76</t>
+          <t>68.44</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.30</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.23</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>68.48</t>
+          <t>68.16</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -5632,7 +5632,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>68.41</t>
+          <t>68.09</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>97.800</t>
+          <t>102.560</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>99.530</t>
+          <t>103.950</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.450</t>
+          <t>104.630</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5816,7 +5816,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104.110</t>
+          <t>107.970</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>106.000</t>
+          <t>109.740</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>106.410</t>
+          <t>109.990</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>104.460</t>
+          <t>107.990</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>96.390</t>
+          <t>99.890</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>85.030</t>
+          <t>87.220</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80.470</t>
+          <t>80.800</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>76.340</t>
+          <t>76.920</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75.850</t>
+          <t>76.500</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>76.740</t>
+          <t>77.390</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77.270</t>
+          <t>78.010</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>77.310</t>
+          <t>78.060</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>80.650</t>
+          <t>81.420</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>81.670</t>
+          <t>82.680</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>83.490</t>
+          <t>83.980</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>83.340</t>
+          <t>83.830</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>77.600</t>
+          <t>78.090</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6356,7 +6356,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>67.840</t>
+          <t>67.880</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70.120</t>
+          <t>70.160</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>72.110</t>
+          <t>72.160</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>74.470</t>
+          <t>74.520</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>74.060</t>
+          <t>74.110</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -6572,7 +6572,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>71.140</t>
+          <t>71.190</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>61.210</t>
+          <t>61.280</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>56.820</t>
+          <t>56.890</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>55.460</t>
+          <t>55.530</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -6680,7 +6680,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>56.130</t>
+          <t>56.200</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>56.220</t>
+          <t>57.020</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -6734,7 +6734,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>57.870</t>
+          <t>58.670</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>62.960</t>
+          <t>63.760</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>64.930</t>
+          <t>65.730</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>66.800</t>
+          <t>67.600</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>67.730</t>
+          <t>68.690</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>68.730</t>
+          <t>69.690</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>67.720</t>
+          <t>68.680</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>62.550</t>
+          <t>63.510</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -6950,7 +6950,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>59.760</t>
+          <t>60.720</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>57.160</t>
+          <t>58.120</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>54.830</t>
+          <t>55.790</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>53.420</t>
+          <t>54.380</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>54.430</t>
+          <t>55.390</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>62.960</t>
+          <t>63.920</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>65.550</t>
+          <t>66.510</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>67.440</t>
+          <t>68.400</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>68.660</t>
+          <t>69.620</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>68.990</t>
+          <t>69.950</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>67.480</t>
+          <t>68.440</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>62.870</t>
+          <t>63.830</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>58.770</t>
+          <t>59.730</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>56.170</t>
+          <t>57.130</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>54.740</t>
+          <t>55.700</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>54.030</t>
+          <t>54.990</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>55.050</t>
+          <t>56.010</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>60.360</t>
+          <t>61.320</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>63.030</t>
+          <t>63.990</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>65.580</t>
+          <t>66.540</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>15.525</t>
+          <t>15.820</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14.960</t>
+          <t>15.740</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>14.510</t>
+          <t>15.115</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -7647,7 +7647,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14.330</t>
+          <t>14.920</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>14.400</t>
+          <t>14.925</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -7701,7 +7701,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14.205</t>
+          <t>14.720</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>13.840</t>
+          <t>14.320</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -7755,7 +7755,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12.995</t>
+          <t>13.460</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7782,7 +7782,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>11.675</t>
+          <t>11.905</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -7809,7 +7809,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11.185</t>
+          <t>11.310</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>11.260</t>
+          <t>11.360</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -7863,7 +7863,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11.405</t>
+          <t>11.490</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>11.470</t>
+          <t>11.550</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11.480</t>
+          <t>11.565</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>11.450</t>
+          <t>11.545</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11.435</t>
+          <t>11.535</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>11.740</t>
+          <t>11.810</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -8025,7 +8025,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11.770</t>
+          <t>11.800</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>11.550</t>
+          <t>11.585</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10.795</t>
+          <t>10.825</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>9.860</t>
+          <t>9.875</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9.455</t>
+          <t>9.470</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>9.415</t>
+          <t>9.430</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -8187,7 +8187,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9.390</t>
+          <t>9.410</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>9.330</t>
+          <t>9.350</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -8241,7 +8241,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9.370</t>
+          <t>9.385</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>9.325</t>
+          <t>9.345</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -8295,7 +8295,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9.450</t>
+          <t>9.465</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>9.705</t>
+          <t>9.720</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10.640</t>
+          <t>10.675</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>10.445</t>
+          <t>10.480</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>9.760</t>
+          <t>9.795</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>8.915</t>
+          <t>8.935</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -8457,7 +8457,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8.550</t>
+          <t>8.565</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>8.510</t>
+          <t>8.530</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8.490</t>
+          <t>8.510</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>8.435</t>
+          <t>8.455</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>8.470</t>
+          <t>8.490</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>8.430</t>
+          <t>8.455</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>8.540</t>
+          <t>8.565</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>8.775</t>
+          <t>8.795</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>9.980</t>
+          <t>10.030</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>9.795</t>
+          <t>9.845</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -8727,7 +8727,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>9.155</t>
+          <t>9.200</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>8.360</t>
+          <t>8.395</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -8781,7 +8781,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>8.015</t>
+          <t>8.045</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>7.980</t>
+          <t>8.010</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>7.965</t>
+          <t>7.995</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>7.910</t>
+          <t>7.945</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -8889,7 +8889,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>7.945</t>
+          <t>7.975</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>7.905</t>
+          <t>7.940</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -8943,7 +8943,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>8.010</t>
+          <t>8.045</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>8.230</t>
+          <t>8.260</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8997,7 +8997,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>9.320</t>
+          <t>9.380</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>9.145</t>
+          <t>9.205</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>8.550</t>
+          <t>8.605</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>7.805</t>
+          <t>7.850</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9105,7 +9105,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>7.485</t>
+          <t>7.525</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>7.455</t>
+          <t>7.495</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9159,7 +9159,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>7.435</t>
+          <t>7.475</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>7.390</t>
+          <t>7.430</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>7.420</t>
+          <t>7.460</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>7.385</t>
+          <t>7.425</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>7.480</t>
+          <t>7.525</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>7.685</t>
+          <t>7.725</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -9370,7 +9370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>40.782</t>
+          <t>42.565</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.842</t>
+          <t>42.616</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41.087</t>
+          <t>43.675</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>41.068</t>
+          <t>42.642</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -9478,7 +9478,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.728</t>
+          <t>42.247</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>40.683</t>
+          <t>42.176</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.437</t>
+          <t>41.880</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>39.817</t>
+          <t>41.135</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -9586,7 +9586,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38.327</t>
+          <t>39.499</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>33.817</t>
+          <t>34.451</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -9640,7 +9640,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32.184</t>
+          <t>32.509</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>31.779</t>
+          <t>32.023</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -9694,7 +9694,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31.700</t>
+          <t>31.948</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>31.701</t>
+          <t>31.943</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31.766</t>
+          <t>32.013</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>31.461</t>
+          <t>31.675</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -9802,7 +9802,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31.600</t>
+          <t>31.820</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>32.020</t>
+          <t>32.160</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -9856,7 +9856,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31.892</t>
+          <t>31.950</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>31.367</t>
+          <t>31.425</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>29.927</t>
+          <t>29.980</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>27.022</t>
+          <t>27.040</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -9964,7 +9964,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25.883</t>
+          <t>25.895</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>25.588</t>
+          <t>25.600</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -10018,7 +10018,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25.491</t>
+          <t>25.510</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>25.361</t>
+          <t>25.380</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -10072,7 +10072,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>25.511</t>
+          <t>25.530</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>25.718</t>
+          <t>25.745</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -10126,7 +10126,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26.188</t>
+          <t>26.210</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>26.607</t>
+          <t>26.620</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -10180,7 +10180,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>27.034</t>
+          <t>27.054</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>27.249</t>
+          <t>27.264</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -10234,7 +10234,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>26.584</t>
+          <t>26.594</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>23.429</t>
+          <t>23.567</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -10288,7 +10288,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>22.909</t>
+          <t>23.047</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>22.474</t>
+          <t>22.607</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -10342,7 +10342,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>21.994</t>
+          <t>22.127</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>22.084</t>
+          <t>22.217</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>22.579</t>
+          <t>22.717</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>22.693</t>
+          <t>22.829</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>23.093</t>
+          <t>23.234</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -10477,7 +10477,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>23.468</t>
+          <t>23.604</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -10504,7 +10504,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>23.688</t>
+          <t>23.734</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>23.643</t>
+          <t>23.690</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -10558,7 +10558,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>23.608</t>
+          <t>23.656</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>21.798</t>
+          <t>21.831</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>21.378</t>
+          <t>21.437</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>20.923</t>
+          <t>21.007</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -10666,7 +10666,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>19.918</t>
+          <t>20.027</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10693,7 +10693,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>20.268</t>
+          <t>20.383</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -10720,7 +10720,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>20.933</t>
+          <t>21.049</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10747,7 +10747,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>21.673</t>
+          <t>21.724</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -10774,7 +10774,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>22.448</t>
+          <t>22.499</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>22.878</t>
+          <t>22.924</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -10828,7 +10828,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>23.118</t>
+          <t>23.164</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>22.928</t>
+          <t>22.979</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>22.703</t>
+          <t>22.754</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>21.980</t>
+          <t>21.769</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>21.505</t>
+          <t>21.294</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>21.250</t>
+          <t>21.034</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>20.485</t>
+          <t>20.269</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>20.670</t>
+          <t>20.454</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>21.160</t>
+          <t>20.944</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>22.450</t>
+          <t>22.134</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -11098,7 +11098,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>23.145</t>
+          <t>22.829</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>23.525</t>
+          <t>23.204</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -11152,7 +11152,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>23.045</t>
+          <t>22.619</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>22.906</t>
+          <t>22.474</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>22.806</t>
+          <t>22.374</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>22.976</t>
+          <t>22.849</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>22.656</t>
+          <t>22.529</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>22.101</t>
+          <t>21.974</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>21.751</t>
+          <t>21.624</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>22.196</t>
+          <t>22.064</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>22.731</t>
+          <t>22.599</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>23.526</t>
+          <t>23.394</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>23.881</t>
+          <t>23.749</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>24.056</t>
+          <t>23.924</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -11476,7 +11476,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>25.011</t>
+          <t>24.879</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>24.901</t>
+          <t>24.769</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -11530,7 +11530,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>24.716</t>
+          <t>24.584</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>24.351</t>
+          <t>24.219</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -11584,7 +11584,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>23.896</t>
+          <t>23.764</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -11611,7 +11611,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>23.541</t>
+          <t>23.409</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -11638,7 +11638,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>23.266</t>
+          <t>23.134</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>23.716</t>
+          <t>23.584</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -11692,7 +11692,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>24.111</t>
+          <t>23.979</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>24.711</t>
+          <t>24.579</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -11746,7 +11746,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>25.211</t>
+          <t>25.079</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>25.386</t>
+          <t>25.254</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>26.336</t>
+          <t>26.204</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>26.241</t>
+          <t>26.109</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>26.061</t>
+          <t>25.929</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>25.891</t>
+          <t>25.759</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>25.391</t>
+          <t>25.259</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>25.091</t>
+          <t>24.959</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>24.891</t>
+          <t>24.759</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>25.291</t>
+          <t>25.159</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -12016,7 +12016,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>25.686</t>
+          <t>25.554</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>26.286</t>
+          <t>26.154</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HH" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Brent" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="NBP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="JKM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TTF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cotações Diárias" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HH" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Brent" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NBP" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="JKM" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TTF" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +39,10 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +104,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,6 +477,818 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002E86AB"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>HH</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>NBP</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>JKM</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>TTF</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Coal_API2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>3.1790</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>94.9800</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>119.0900</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>18.6850</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>49.0900</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>3.1670</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>96.0000</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>114.7900</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>18.6100</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>47.6070</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>3.2140</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>97.8100</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>117.9000</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>18.8150</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>48.8640</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>3.3360</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>95.0300</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>117.9300</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>18.7650</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>48.7520</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>3.2290</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>93.0900</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>117.0500</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>18.7750</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>48.4960</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>3.1470</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>94.2500</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>120.5300</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>18.8950</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>49.8260</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>3.1400</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>91.4500</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>117.1900</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>18.8850</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>48.7440</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>3.1850</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>93.1000</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>120.3200</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>18.9150</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>49.9890</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>3.0870</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>90.3800</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>119.7600</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>18.9200</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>49.6900</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>3.1200</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>87.3300</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>111.9100</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>18.8550</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>46.7730</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>3.1470</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>83.1700</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>101.0100</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>18.7830</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>42.5070</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>3.2390</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>78.9600</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>99.4000</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>15.9400</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>41.7690</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>3.1450</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>79.5500</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>99.7800</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>15.8200</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>41.9150</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>3.2330</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>79.8500</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>96.6900</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>15.3150</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>40.5230</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>3.2530</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>77.9000</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>99.9400</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>15.8600</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>41.8870</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>3.1470</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>77.0800</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>100.2900</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>15.7400</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>42.0140</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>3.2210</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>73.7400</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>97.1800</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>15.5500</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>40.8760</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>3.3430</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>75.2600</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>96.5200</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>15.3850</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>40.4050</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>3.2310</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>71.9900</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>97.8000</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>15.5250</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>40.7820</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>3.1810</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>73.1500</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>102.6100</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>15.8200</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>42.5650</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>3.2750</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>72.9200</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>104.4500</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>16.0500</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>43.4440</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>3.2200</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>71.5700</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>101.6900</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>16.0250</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>42.7790</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>3.1640</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>70.8000</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>43.9950</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -8609,7 +9435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C00"/>
@@ -15867,7 +16693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00375623"/>
@@ -21262,7 +22088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -26603,7 +27429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C55A11"/>

--- a/data/CME_Futures_Database.xlsx
+++ b/data/CME_Futures_Database.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,6 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -524,374 +523,350 @@
           <t>TTF</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Coal_API2</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>3.1790</t>
+          <t>3.1910</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>94.9800</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>119.0900</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>18.6850</t>
-        </is>
-      </c>
+          <t>70.7000</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>49.0900</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr"/>
+          <t>43.9950</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>3.1670</t>
+          <t>3.2200</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>96.0000</t>
+          <t>71.5700</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>114.7900</t>
+          <t>101.6900</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>18.6100</t>
+          <t>16.0250</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>47.6070</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr"/>
+          <t>42.7790</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>3.2140</t>
+          <t>3.2750</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>97.8100</t>
+          <t>72.9200</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>117.9000</t>
+          <t>104.4500</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>18.8150</t>
+          <t>16.0500</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>48.8640</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
+          <t>43.4440</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>3.3360</t>
+          <t>3.1810</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>95.0300</t>
+          <t>73.1500</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>117.9300</t>
+          <t>102.6100</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>18.7650</t>
+          <t>15.8200</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>48.7520</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
+          <t>42.5650</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3.2290</t>
+          <t>3.2310</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>93.0900</t>
+          <t>71.9900</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>117.0500</t>
+          <t>97.8000</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>18.7750</t>
+          <t>15.5250</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>48.4960</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr"/>
+          <t>40.7820</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>3.1470</t>
+          <t>3.3430</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>94.2500</t>
+          <t>75.2600</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>120.5300</t>
+          <t>96.5200</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>18.8950</t>
+          <t>15.3850</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>49.8260</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
+          <t>40.4050</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>3.1400</t>
+          <t>3.2210</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>91.4500</t>
+          <t>73.7400</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>117.1900</t>
+          <t>97.1800</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>18.8850</t>
+          <t>15.5500</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>48.7440</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>40.8760</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>3.1850</t>
+          <t>3.1470</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>93.1000</t>
+          <t>77.0800</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>120.3200</t>
+          <t>100.2900</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>18.9150</t>
+          <t>15.7400</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>49.9890</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
+          <t>42.0140</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>3.0870</t>
+          <t>3.2530</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>90.3800</t>
+          <t>77.9000</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>119.7600</t>
+          <t>99.9400</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>18.9200</t>
+          <t>15.8600</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>49.6900</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
+          <t>41.8870</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>3.1200</t>
+          <t>3.2330</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>87.3300</t>
+          <t>79.8500</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>111.9100</t>
+          <t>96.6900</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>18.8550</t>
+          <t>15.3150</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>46.7730</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr"/>
+          <t>40.5230</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>3.1470</t>
+          <t>3.1450</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>83.1700</t>
+          <t>79.5500</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>101.0100</t>
+          <t>99.7800</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>18.7830</t>
+          <t>15.8200</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>42.5070</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
+          <t>41.9150</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -924,362 +899,358 @@
           <t>41.7690</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>3.1450</t>
+          <t>3.1470</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>79.5500</t>
+          <t>83.1700</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>99.7800</t>
+          <t>101.0100</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>15.8200</t>
+          <t>18.7830</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>41.9150</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
+          <t>42.5070</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>3.2330</t>
+          <t>3.1200</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>79.8500</t>
+          <t>87.3300</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>96.6900</t>
+          <t>111.9100</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>15.3150</t>
+          <t>18.8550</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>40.5230</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr"/>
+          <t>46.7730</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>3.2530</t>
+          <t>3.0870</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>77.9000</t>
+          <t>90.3800</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>99.9400</t>
+          <t>119.7600</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>15.8600</t>
+          <t>18.9200</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>41.8870</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
+          <t>49.6900</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>3.1470</t>
+          <t>3.1850</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>77.0800</t>
+          <t>93.1000</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>100.2900</t>
+          <t>120.3200</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>15.7400</t>
+          <t>18.9150</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>42.0140</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr"/>
+          <t>49.9890</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>3.2210</t>
+          <t>3.1400</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>73.7400</t>
+          <t>91.4500</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>97.1800</t>
+          <t>117.1900</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>15.5500</t>
+          <t>18.8850</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>40.8760</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
+          <t>48.7440</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>3.3430</t>
+          <t>3.1470</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>75.2600</t>
+          <t>94.2500</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>96.5200</t>
+          <t>120.5300</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>15.3850</t>
+          <t>18.8950</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>40.4050</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
+          <t>49.8260</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>3.2310</t>
+          <t>3.2290</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>71.9900</t>
+          <t>93.0900</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>97.8000</t>
+          <t>117.0500</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>15.5250</t>
+          <t>18.7750</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>40.7820</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
+          <t>48.4960</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>3.1810</t>
+          <t>3.3360</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>73.1500</t>
+          <t>95.0300</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>102.6100</t>
+          <t>117.9300</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>15.8200</t>
+          <t>18.7650</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>42.5650</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr"/>
+          <t>48.7520</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>3.2750</t>
+          <t>3.2140</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>72.9200</t>
+          <t>97.8100</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>104.4500</t>
+          <t>117.9000</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>16.0500</t>
+          <t>18.8150</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>43.4440</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
+          <t>48.8640</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>3.2200</t>
+          <t>3.1670</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>71.5700</t>
+          <t>96.0000</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>101.6900</t>
+          <t>114.7900</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>16.0250</t>
+          <t>18.6100</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>42.7790</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
+          <t>47.6070</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>3.1910</t>
+          <t>3.1790</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>70.7000</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
+          <t>94.9800</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>119.0900</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>18.6850</t>
+        </is>
+      </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>43.9950</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
+          <t>49.0900</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
